--- a/outputs/features1.xlsx
+++ b/outputs/features1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alna7\Downloads\latestanemia\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alna7\Downloads\anemiaapp\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60875A90-9103-499B-8563-3711DD171341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27114DE1-AB51-4F41-8B28-B11C44119556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1284" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
   <si>
     <t>filename</t>
   </si>
@@ -244,25 +244,229 @@
     <t>150.jpg</t>
   </si>
   <si>
+    <t>151.jpg</t>
+  </si>
+  <si>
+    <t>152.jpg</t>
+  </si>
+  <si>
+    <t>153.jpg</t>
+  </si>
+  <si>
+    <t>154.jpg</t>
+  </si>
+  <si>
+    <t>155.jpg</t>
+  </si>
+  <si>
+    <t>156.jpg</t>
+  </si>
+  <si>
+    <t>157.jpg</t>
+  </si>
+  <si>
+    <t>158.jpg</t>
+  </si>
+  <si>
+    <t>159.jpg</t>
+  </si>
+  <si>
     <t>16.jpg</t>
   </si>
   <si>
+    <t>160.jpg</t>
+  </si>
+  <si>
+    <t>161.jpg</t>
+  </si>
+  <si>
+    <t>162.jpg</t>
+  </si>
+  <si>
+    <t>163.jpg</t>
+  </si>
+  <si>
+    <t>164.jpg</t>
+  </si>
+  <si>
+    <t>165.jpg</t>
+  </si>
+  <si>
+    <t>166.jpg</t>
+  </si>
+  <si>
+    <t>167.jpg</t>
+  </si>
+  <si>
+    <t>168.jpg</t>
+  </si>
+  <si>
+    <t>169.jpg</t>
+  </si>
+  <si>
     <t>17.jpg</t>
   </si>
   <si>
+    <t>170.jpg</t>
+  </si>
+  <si>
+    <t>171.jpg</t>
+  </si>
+  <si>
+    <t>172.jpg</t>
+  </si>
+  <si>
+    <t>173.jpg</t>
+  </si>
+  <si>
+    <t>174.jpg</t>
+  </si>
+  <si>
+    <t>175.jpg</t>
+  </si>
+  <si>
+    <t>176.jpg</t>
+  </si>
+  <si>
+    <t>177.jpg</t>
+  </si>
+  <si>
+    <t>178.jpg</t>
+  </si>
+  <si>
+    <t>179.jpg</t>
+  </si>
+  <si>
     <t>18.jpg</t>
   </si>
   <si>
+    <t>180.jpg</t>
+  </si>
+  <si>
+    <t>181.jpg</t>
+  </si>
+  <si>
+    <t>182.jpg</t>
+  </si>
+  <si>
+    <t>183.jpg</t>
+  </si>
+  <si>
+    <t>184.jpg</t>
+  </si>
+  <si>
+    <t>185.jpg</t>
+  </si>
+  <si>
+    <t>186.jpg</t>
+  </si>
+  <si>
+    <t>187.jpg</t>
+  </si>
+  <si>
+    <t>188.jpg</t>
+  </si>
+  <si>
+    <t>189.jpg</t>
+  </si>
+  <si>
     <t>19.jpg</t>
   </si>
   <si>
+    <t>190.jpg</t>
+  </si>
+  <si>
+    <t>191.jpg</t>
+  </si>
+  <si>
+    <t>192.jpg</t>
+  </si>
+  <si>
+    <t>193.jpg</t>
+  </si>
+  <si>
+    <t>194.jpg</t>
+  </si>
+  <si>
+    <t>195.jpg</t>
+  </si>
+  <si>
+    <t>196.jpg</t>
+  </si>
+  <si>
+    <t>197.jpg</t>
+  </si>
+  <si>
+    <t>198.jpg</t>
+  </si>
+  <si>
+    <t>199.jpg</t>
+  </si>
+  <si>
     <t>2.jpg</t>
   </si>
   <si>
     <t>20.jpg</t>
   </si>
   <si>
+    <t>200.jpg</t>
+  </si>
+  <si>
+    <t>201.jpg</t>
+  </si>
+  <si>
+    <t>202.jpg</t>
+  </si>
+  <si>
+    <t>203.jpg</t>
+  </si>
+  <si>
+    <t>204.jpg</t>
+  </si>
+  <si>
+    <t>205.jpg</t>
+  </si>
+  <si>
+    <t>206.jpg</t>
+  </si>
+  <si>
+    <t>207.jpg</t>
+  </si>
+  <si>
+    <t>208.jpg</t>
+  </si>
+  <si>
+    <t>209.jpg</t>
+  </si>
+  <si>
     <t>21.jpg</t>
+  </si>
+  <si>
+    <t>210.jpg</t>
+  </si>
+  <si>
+    <t>211.jpg</t>
+  </si>
+  <si>
+    <t>212.jpg</t>
+  </si>
+  <si>
+    <t>213.jpg</t>
+  </si>
+  <si>
+    <t>214.jpg</t>
+  </si>
+  <si>
+    <t>215.jpg</t>
+  </si>
+  <si>
+    <t>216.jpg</t>
+  </si>
+  <si>
+    <t>217.jpg</t>
+  </si>
+  <si>
+    <t>218.jpg</t>
   </si>
   <si>
     <t>22.jpg</t>
@@ -877,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P150"/>
+  <dimension ref="A1:P218"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -3835,49 +4039,49 @@
         <v>74</v>
       </c>
       <c r="B60">
-        <v>13.5</v>
+        <v>11.2</v>
       </c>
       <c r="C60">
-        <v>0.38036808371543879</v>
+        <v>0.37647059559822083</v>
       </c>
       <c r="D60">
-        <v>22.96779823303223</v>
+        <v>22.545076370239261</v>
       </c>
       <c r="E60">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F60">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="G60">
-        <v>1.379031675830793</v>
+        <v>1.3900076984854499</v>
       </c>
       <c r="H60">
-        <v>0.26274511218070978</v>
+        <v>0.29019609093666082</v>
       </c>
       <c r="I60">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J60">
-        <v>1.924923777580261</v>
+        <v>2.4476990699768071</v>
       </c>
       <c r="K60">
-        <v>35.430191040039063</v>
+        <v>43.572811126708977</v>
       </c>
       <c r="L60">
-        <v>146.63423156738281</v>
+        <v>131.2440490722656</v>
       </c>
       <c r="M60">
-        <v>151.93159484863281</v>
+        <v>143.67518615722659</v>
       </c>
       <c r="N60">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="O60">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="P60">
-        <v>1.8972542285919189</v>
+        <v>2.2056093215942378</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
@@ -3885,49 +4089,49 @@
         <v>75</v>
       </c>
       <c r="B61">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="C61">
-        <v>0.3978022038936615</v>
+        <v>0.4080604612827301</v>
       </c>
       <c r="D61">
-        <v>22.649517059326168</v>
+        <v>30.003337860107418</v>
       </c>
       <c r="E61">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="F61">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="G61">
-        <v>1.3983758988558179</v>
+        <v>1.608343781475247</v>
       </c>
       <c r="H61">
-        <v>0.29019609093666082</v>
+        <v>0.3960784375667572</v>
       </c>
       <c r="I61">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="J61">
-        <v>2.2526752948760991</v>
+        <v>3.0235354900360112</v>
       </c>
       <c r="K61">
-        <v>34.692920684814453</v>
+        <v>29.6334342956543</v>
       </c>
       <c r="L61">
-        <v>150.99951171875</v>
+        <v>122.8863525390625</v>
       </c>
       <c r="M61">
-        <v>144.75128173828119</v>
+        <v>136.21675109863281</v>
       </c>
       <c r="N61">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O61">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="P61">
-        <v>2.245625495910645</v>
+        <v>3.2487273216247559</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
@@ -3935,49 +4139,49 @@
         <v>76</v>
       </c>
       <c r="B62">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="C62">
-        <v>0.40993788838386541</v>
+        <v>0.37149026989936829</v>
       </c>
       <c r="D62">
-        <v>28.452554702758789</v>
+        <v>20.330715179443359</v>
       </c>
       <c r="E62">
+        <v>158</v>
+      </c>
+      <c r="F62">
+        <v>61</v>
+      </c>
+      <c r="G62">
+        <v>1.360772212682688</v>
+      </c>
+      <c r="H62">
+        <v>0.30980393290519709</v>
+      </c>
+      <c r="I62">
         <v>198</v>
       </c>
-      <c r="F62">
-        <v>177</v>
-      </c>
-      <c r="G62">
-        <v>1.5104398704420099</v>
-      </c>
-      <c r="H62">
-        <v>0.32941177487373352</v>
-      </c>
-      <c r="I62">
-        <v>189</v>
-      </c>
       <c r="J62">
-        <v>2.27857518196106</v>
+        <v>2.0120968818664551</v>
       </c>
       <c r="K62">
-        <v>29.225004196166989</v>
+        <v>49.25335693359375</v>
       </c>
       <c r="L62">
-        <v>152.2423095703125</v>
+        <v>123.1344451904297</v>
       </c>
       <c r="M62">
-        <v>148.02131652832031</v>
+        <v>134.7090148925781</v>
       </c>
       <c r="N62">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="O62">
         <v>181</v>
       </c>
       <c r="P62">
-        <v>2.1961650848388672</v>
+        <v>1.9616469144821169</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
@@ -3985,49 +4189,49 @@
         <v>77</v>
       </c>
       <c r="B63">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="C63">
-        <v>0.37037035822868353</v>
+        <v>0.364705890417099</v>
       </c>
       <c r="D63">
-        <v>18.94943809509277</v>
+        <v>20.88950157165527</v>
       </c>
       <c r="E63">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="F63">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="G63">
-        <v>1.278400620001662</v>
+        <v>1.343902673646961</v>
       </c>
       <c r="H63">
-        <v>0.23921568691730499</v>
+        <v>0.29411765933036799</v>
       </c>
       <c r="I63">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="J63">
-        <v>2.1344208717346191</v>
+        <v>2.0396633148193359</v>
       </c>
       <c r="K63">
-        <v>37.956794738769531</v>
+        <v>47.893081665039063</v>
       </c>
       <c r="L63">
-        <v>152.48497009277341</v>
+        <v>128.31622314453119</v>
       </c>
       <c r="M63">
-        <v>161.77861022949219</v>
+        <v>144.62017822265619</v>
       </c>
       <c r="N63">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="O63">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="P63">
-        <v>2.083043098449707</v>
+        <v>1.916287779808044</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
@@ -4035,49 +4239,49 @@
         <v>78</v>
       </c>
       <c r="B64">
-        <v>10.199999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="C64">
-        <v>0.35836178064346308</v>
+        <v>0.37441861629486078</v>
       </c>
       <c r="D64">
-        <v>16.692262649536129</v>
+        <v>21.843305587768551</v>
       </c>
       <c r="E64">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="F64">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="G64">
-        <v>1.205726424101178</v>
+        <v>1.3496440295308281</v>
       </c>
       <c r="H64">
-        <v>0.18431372940540311</v>
+        <v>0.28235295414924622</v>
       </c>
       <c r="I64">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="J64">
-        <v>3.2205543518066411</v>
+        <v>2.1514229774475102</v>
       </c>
       <c r="K64">
-        <v>29.026775360107418</v>
+        <v>41.989246368408203</v>
       </c>
       <c r="L64">
-        <v>170.5085754394531</v>
+        <v>130.96983337402341</v>
       </c>
       <c r="M64">
-        <v>183.42027282714841</v>
+        <v>147.42698669433591</v>
       </c>
       <c r="N64">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="O64">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="P64">
-        <v>2.889278888702393</v>
+        <v>2.1495413780212398</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
@@ -4085,49 +4289,49 @@
         <v>79</v>
       </c>
       <c r="B65">
-        <v>13.6</v>
+        <v>11.3</v>
       </c>
       <c r="C65">
-        <v>0.42970821261405939</v>
+        <v>0.35632184147834778</v>
       </c>
       <c r="D65">
-        <v>31.930524826049801</v>
+        <v>19.81887054443359</v>
       </c>
       <c r="E65">
+        <v>174</v>
+      </c>
+      <c r="F65">
+        <v>70</v>
+      </c>
+      <c r="G65">
+        <v>1.27190487152037</v>
+      </c>
+      <c r="H65">
+        <v>0.27058824896812439</v>
+      </c>
+      <c r="I65">
+        <v>207</v>
+      </c>
+      <c r="J65">
+        <v>2.3927278518676758</v>
+      </c>
+      <c r="K65">
+        <v>43.883419036865227</v>
+      </c>
+      <c r="L65">
+        <v>140.6625061035156</v>
+      </c>
+      <c r="M65">
+        <v>161.17390441894531</v>
+      </c>
+      <c r="N65">
+        <v>97</v>
+      </c>
+      <c r="O65">
         <v>192</v>
       </c>
-      <c r="F65">
-        <v>169</v>
-      </c>
-      <c r="G65">
-        <v>1.6116149563817701</v>
-      </c>
-      <c r="H65">
-        <v>0.40392157435417181</v>
-      </c>
-      <c r="I65">
-        <v>194</v>
-      </c>
-      <c r="J65">
-        <v>2.3849482536315918</v>
-      </c>
-      <c r="K65">
-        <v>33.672168731689453</v>
-      </c>
-      <c r="L65">
-        <v>143.1998291015625</v>
-      </c>
-      <c r="M65">
-        <v>143.0824279785156</v>
-      </c>
-      <c r="N65">
-        <v>91</v>
-      </c>
-      <c r="O65">
-        <v>175</v>
-      </c>
       <c r="P65">
-        <v>2.3251838684082031</v>
+        <v>2.20564866065979</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
@@ -4135,49 +4339,49 @@
         <v>80</v>
       </c>
       <c r="B66">
-        <v>9.8000000000000007</v>
+        <v>11.4</v>
       </c>
       <c r="C66">
-        <v>0.38679245114326483</v>
+        <v>0.36923077702522278</v>
       </c>
       <c r="D66">
-        <v>21.161613464355469</v>
+        <v>17.58793830871582</v>
       </c>
       <c r="E66">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="F66">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="G66">
-        <v>1.3215298205311521</v>
+        <v>1.2706686821737541</v>
       </c>
       <c r="H66">
-        <v>0.27058824896812439</v>
+        <v>0.25490197539329529</v>
       </c>
       <c r="I66">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="J66">
-        <v>3.2145519256591801</v>
+        <v>2.2105274200439449</v>
       </c>
       <c r="K66">
-        <v>39.887115478515618</v>
+        <v>40.9176025390625</v>
       </c>
       <c r="L66">
-        <v>155.17970275878909</v>
+        <v>129.7287902832031</v>
       </c>
       <c r="M66">
-        <v>162.68360900878909</v>
+        <v>143.26307678222659</v>
       </c>
       <c r="N66">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O66">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="P66">
-        <v>2.5131568908691411</v>
+        <v>2.1432981491088872</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
@@ -4185,49 +4389,49 @@
         <v>81</v>
       </c>
       <c r="B67">
-        <v>12.6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="C67">
-        <v>0.39056605100631708</v>
+        <v>0.34704369306564331</v>
       </c>
       <c r="D67">
-        <v>24.4166259765625</v>
+        <v>17.794378280639648</v>
       </c>
       <c r="E67">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="F67">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="G67">
-        <v>1.386543748364379</v>
+        <v>1.259109105433817</v>
       </c>
       <c r="H67">
-        <v>0.28235295414924622</v>
+        <v>0.27058824896812439</v>
       </c>
       <c r="I67">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J67">
-        <v>4.0210552215576172</v>
+        <v>2.0856795310974121</v>
       </c>
       <c r="K67">
-        <v>28.030525207519531</v>
+        <v>46.767143249511719</v>
       </c>
       <c r="L67">
-        <v>160.51799011230469</v>
+        <v>127.5235214233398</v>
       </c>
       <c r="M67">
-        <v>164.1476135253906</v>
+        <v>147.0362548828125</v>
       </c>
       <c r="N67">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="O67">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="P67">
-        <v>3.0694296360015869</v>
+        <v>2.1157073974609379</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
@@ -4235,49 +4439,49 @@
         <v>82</v>
       </c>
       <c r="B68">
-        <v>9.6</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="C68">
-        <v>0.37234041094779968</v>
+        <v>0.37638375163078308</v>
       </c>
       <c r="D68">
-        <v>20.99424934387207</v>
+        <v>21.8954963684082</v>
       </c>
       <c r="E68">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F68">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G68">
-        <v>1.323239914226507</v>
+        <v>1.326060101374952</v>
       </c>
       <c r="H68">
-        <v>0.27058824896812439</v>
+        <v>0.29411765933036799</v>
       </c>
       <c r="I68">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="J68">
-        <v>2.3628542423248291</v>
+        <v>2.1055464744567871</v>
       </c>
       <c r="K68">
-        <v>42.522579193115227</v>
+        <v>42.654991149902337</v>
       </c>
       <c r="L68">
-        <v>143.60475158691409</v>
+        <v>135.58613586425781</v>
       </c>
       <c r="M68">
-        <v>155.12562561035159</v>
+        <v>155.14404296875</v>
       </c>
       <c r="N68">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O68">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="P68">
-        <v>2.0149791240692139</v>
+        <v>1.92353367805481</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
@@ -4285,49 +4489,49 @@
         <v>83</v>
       </c>
       <c r="B69">
-        <v>9.1999999999999993</v>
+        <v>13.5</v>
       </c>
       <c r="C69">
-        <v>0.37330755591392523</v>
+        <v>0.38036808371543879</v>
       </c>
       <c r="D69">
-        <v>22.324651718139648</v>
+        <v>22.96779823303223</v>
       </c>
       <c r="E69">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F69">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="G69">
-        <v>1.328698859560999</v>
+        <v>1.379031675830793</v>
       </c>
       <c r="H69">
-        <v>0.23921568691730499</v>
+        <v>0.26274511218070978</v>
       </c>
       <c r="I69">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="J69">
-        <v>3.1383018493652339</v>
+        <v>1.924923777580261</v>
       </c>
       <c r="K69">
-        <v>23.788957595825199</v>
+        <v>35.430191040039063</v>
       </c>
       <c r="L69">
-        <v>156.7457275390625</v>
+        <v>146.63423156738281</v>
       </c>
       <c r="M69">
-        <v>168.5501708984375</v>
+        <v>151.93159484863281</v>
       </c>
       <c r="N69">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="O69">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P69">
-        <v>2.5668244361877441</v>
+        <v>1.8972542285919189</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
@@ -4335,49 +4539,49 @@
         <v>84</v>
       </c>
       <c r="B70">
-        <v>8.6999999999999993</v>
+        <v>12.7</v>
       </c>
       <c r="C70">
-        <v>0.34565618634223938</v>
+        <v>0.38565891981124878</v>
       </c>
       <c r="D70">
-        <v>14.27551364898682</v>
+        <v>25.031797409057621</v>
       </c>
       <c r="E70">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F70">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="G70">
-        <v>1.167221924727379</v>
+        <v>1.4044921473677701</v>
       </c>
       <c r="H70">
-        <v>0.18823529779911041</v>
+        <v>0.31372550129890442</v>
       </c>
       <c r="I70">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="J70">
-        <v>2.3267571926116939</v>
+        <v>2.70135498046875</v>
       </c>
       <c r="K70">
-        <v>34.443943023681641</v>
+        <v>32.750446319580078</v>
       </c>
       <c r="L70">
-        <v>160.14442443847659</v>
+        <v>141.5399475097656</v>
       </c>
       <c r="M70">
-        <v>173.73362731933591</v>
+        <v>156.44508361816409</v>
       </c>
       <c r="N70">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="O70">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="P70">
-        <v>1.891933917999268</v>
+        <v>2.4076159000396729</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
@@ -4385,49 +4589,49 @@
         <v>85</v>
       </c>
       <c r="B71">
-        <v>8.6</v>
+        <v>11.1</v>
       </c>
       <c r="C71">
-        <v>0.34963768720626831</v>
+        <v>0.36832061409950262</v>
       </c>
       <c r="D71">
-        <v>15.769749641418461</v>
+        <v>21.441396713256839</v>
       </c>
       <c r="E71">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="F71">
-        <v>154</v>
+        <v>90</v>
       </c>
       <c r="G71">
-        <v>1.1833553271749839</v>
+        <v>1.3505143949931191</v>
       </c>
       <c r="H71">
-        <v>0.18431372940540311</v>
+        <v>0.28627452254295349</v>
       </c>
       <c r="I71">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="J71">
-        <v>2.8535563945770259</v>
+        <v>2.330680131912231</v>
       </c>
       <c r="K71">
-        <v>38.438037872314453</v>
+        <v>39.953506469726563</v>
       </c>
       <c r="L71">
-        <v>167.5732727050781</v>
+        <v>130.51216125488281</v>
       </c>
       <c r="M71">
-        <v>182.7944030761719</v>
+        <v>146.36346435546881</v>
       </c>
       <c r="N71">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="O71">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="P71">
-        <v>2.2124092578887939</v>
+        <v>2.4929606914520259</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
@@ -4435,49 +4639,49 @@
         <v>86</v>
       </c>
       <c r="B72">
-        <v>9.4</v>
+        <v>15.2</v>
       </c>
       <c r="C72">
-        <v>0.37581700086593628</v>
+        <v>0.37396121025085449</v>
       </c>
       <c r="D72">
-        <v>24.49101448059082</v>
+        <v>20.444328308105469</v>
       </c>
       <c r="E72">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="F72">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="G72">
-        <v>1.3977199622229171</v>
+        <v>1.3769726344693001</v>
       </c>
       <c r="H72">
-        <v>0.26666668057441711</v>
+        <v>0.31372550129890442</v>
       </c>
       <c r="I72">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J72">
-        <v>2.2189610004425049</v>
+        <v>2.417412281036377</v>
       </c>
       <c r="K72">
-        <v>32.639450073242188</v>
+        <v>45.759918212890618</v>
       </c>
       <c r="L72">
-        <v>147.292724609375</v>
+        <v>116.08998107910161</v>
       </c>
       <c r="M72">
-        <v>156.4488830566406</v>
+        <v>128.7266845703125</v>
       </c>
       <c r="N72">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="O72">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="P72">
-        <v>2.1850626468658452</v>
+        <v>2.4444434642791748</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
@@ -4485,49 +4689,49 @@
         <v>87</v>
       </c>
       <c r="B73">
-        <v>15.5</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="C73">
-        <v>0.39426523447036738</v>
+        <v>0.3611111044883728</v>
       </c>
       <c r="D73">
-        <v>23.908050537109379</v>
+        <v>17.471096038818359</v>
       </c>
       <c r="E73">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="F73">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="G73">
-        <v>1.3964074946466589</v>
+        <v>1.259860327860584</v>
       </c>
       <c r="H73">
-        <v>0.31372550129890442</v>
+        <v>0.25490197539329529</v>
       </c>
       <c r="I73">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="J73">
-        <v>1.7796592712402339</v>
+        <v>2.3054490089416499</v>
       </c>
       <c r="K73">
-        <v>47.499233245849609</v>
+        <v>42.97076416015625</v>
       </c>
       <c r="L73">
-        <v>148.44252014160159</v>
+        <v>128.51319885253909</v>
       </c>
       <c r="M73">
-        <v>152.2867736816406</v>
+        <v>145.5828552246094</v>
       </c>
       <c r="N73">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="O73">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="P73">
-        <v>1.6866122484207151</v>
+        <v>2.152060747146606</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
@@ -4535,49 +4739,49 @@
         <v>88</v>
       </c>
       <c r="B74">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="C74">
-        <v>0.3684210479259491</v>
+        <v>0.3730158805847168</v>
       </c>
       <c r="D74">
-        <v>21.066268920898441</v>
+        <v>21.594028472900391</v>
       </c>
       <c r="E74">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="F74">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="G74">
-        <v>1.287546069254482</v>
+        <v>1.350113400521314</v>
       </c>
       <c r="H74">
-        <v>0.22745098173618319</v>
+        <v>0.29803922772407532</v>
       </c>
       <c r="I74">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="J74">
-        <v>2.763277530670166</v>
+        <v>2.6244621276855469</v>
       </c>
       <c r="K74">
-        <v>31.858089447021481</v>
+        <v>36.867744445800781</v>
       </c>
       <c r="L74">
-        <v>164.2817687988281</v>
+        <v>135.30070495605469</v>
       </c>
       <c r="M74">
-        <v>176.49797058105469</v>
+        <v>150.1223449707031</v>
       </c>
       <c r="N74">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="O74">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="P74">
-        <v>2.446611642837524</v>
+        <v>2.665216207504272</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
@@ -4585,49 +4789,49 @@
         <v>89</v>
       </c>
       <c r="B75">
-        <v>10.7</v>
+        <v>8.1</v>
       </c>
       <c r="C75">
-        <v>0.36293435096740723</v>
+        <v>0.37284481525421143</v>
       </c>
       <c r="D75">
-        <v>18.719144821166989</v>
+        <v>19.235322952270511</v>
       </c>
       <c r="E75">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="F75">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="G75">
-        <v>1.257477793388714</v>
+        <v>1.305208396403577</v>
       </c>
       <c r="H75">
-        <v>0.20000000298023221</v>
+        <v>0.26274511218070978</v>
       </c>
       <c r="I75">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="J75">
-        <v>2.7884328365325932</v>
+        <v>2.299466609954834</v>
       </c>
       <c r="K75">
-        <v>28.98776817321777</v>
+        <v>41.84222412109375</v>
       </c>
       <c r="L75">
-        <v>162.92198181152341</v>
+        <v>132.56280517578119</v>
       </c>
       <c r="M75">
-        <v>172.64253234863281</v>
+        <v>145.4344787597656</v>
       </c>
       <c r="N75">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="O75">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="P75">
-        <v>2.6085000038146968</v>
+        <v>2.1875348091125488</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
@@ -4635,49 +4839,49 @@
         <v>90</v>
       </c>
       <c r="B76">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="C76">
-        <v>0.39842209219932562</v>
+        <v>0.38333332538604742</v>
       </c>
       <c r="D76">
-        <v>22.51210784912109</v>
+        <v>25.135341644287109</v>
       </c>
       <c r="E76">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="F76">
-        <v>166</v>
+        <v>97</v>
       </c>
       <c r="G76">
-        <v>1.324099004800513</v>
+        <v>1.4459444894965849</v>
       </c>
       <c r="H76">
-        <v>0.30196079611778259</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="I76">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="J76">
-        <v>2.149960994720459</v>
+        <v>2.5237023830413818</v>
       </c>
       <c r="K76">
-        <v>31.642568588256839</v>
+        <v>43.493965148925781</v>
       </c>
       <c r="L76">
-        <v>162.47163391113281</v>
+        <v>132.4934387207031</v>
       </c>
       <c r="M76">
-        <v>171.57289123535159</v>
+        <v>144.91387939453119</v>
       </c>
       <c r="N76">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="O76">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="P76">
-        <v>2.0069327354431148</v>
+        <v>2.4117064476013179</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
@@ -4685,49 +4889,49 @@
         <v>91</v>
       </c>
       <c r="B77">
-        <v>14.8</v>
+        <v>9.6</v>
       </c>
       <c r="C77">
-        <v>0.38576778769493097</v>
+        <v>0.37674418091773992</v>
       </c>
       <c r="D77">
-        <v>25.596847534179691</v>
+        <v>16.231708526611332</v>
       </c>
       <c r="E77">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="F77">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="G77">
-        <v>1.3996312464720591</v>
+        <v>1.2672265693038269</v>
       </c>
       <c r="H77">
-        <v>0.27450981736183172</v>
+        <v>0.2431372553110123</v>
       </c>
       <c r="I77">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="J77">
-        <v>2.0422277450561519</v>
+        <v>2.7623016834259029</v>
       </c>
       <c r="K77">
-        <v>40.588550567626953</v>
+        <v>36.210586547851563</v>
       </c>
       <c r="L77">
-        <v>162.68666076660159</v>
+        <v>135.1723937988281</v>
       </c>
       <c r="M77">
-        <v>165.9930114746094</v>
+        <v>141.7532653808594</v>
       </c>
       <c r="N77">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O77">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="P77">
-        <v>1.9310842752456669</v>
+        <v>2.371246337890625</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.3">
@@ -4735,49 +4939,49 @@
         <v>92</v>
       </c>
       <c r="B78">
-        <v>14.1</v>
+        <v>10</v>
       </c>
       <c r="C78">
-        <v>0.40000000596046448</v>
+        <v>0.35697939991950989</v>
       </c>
       <c r="D78">
-        <v>27.58709716796875</v>
+        <v>15.50057315826416</v>
       </c>
       <c r="E78">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="F78">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="G78">
-        <v>1.4850146948342</v>
+        <v>1.219451768248808</v>
       </c>
       <c r="H78">
-        <v>0.34509804844856262</v>
+        <v>0.21960784494876859</v>
       </c>
       <c r="I78">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="J78">
-        <v>1.9744527339935301</v>
+        <v>2.350387334823608</v>
       </c>
       <c r="K78">
-        <v>40.606281280517578</v>
+        <v>39.783348083496087</v>
       </c>
       <c r="L78">
-        <v>143.5341796875</v>
+        <v>135.26812744140619</v>
       </c>
       <c r="M78">
-        <v>149.8087463378906</v>
+        <v>149.9632568359375</v>
       </c>
       <c r="N78">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="O78">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="P78">
-        <v>1.930024147033691</v>
+        <v>2.386687278747559</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
@@ -4785,49 +4989,49 @@
         <v>93</v>
       </c>
       <c r="B79">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>0.38216561079025269</v>
+        <v>0.35872235894203192</v>
       </c>
       <c r="D79">
-        <v>23.495622634887699</v>
+        <v>17.46310997009277</v>
       </c>
       <c r="E79">
+        <v>166</v>
+      </c>
+      <c r="F79">
+        <v>100</v>
+      </c>
+      <c r="G79">
+        <v>1.265132441795259</v>
+      </c>
+      <c r="H79">
+        <v>0.23921568691730499</v>
+      </c>
+      <c r="I79">
         <v>189</v>
       </c>
-      <c r="F79">
-        <v>136</v>
-      </c>
-      <c r="G79">
-        <v>1.372417098501225</v>
-      </c>
-      <c r="H79">
-        <v>0.29803922772407532</v>
-      </c>
-      <c r="I79">
-        <v>211</v>
-      </c>
       <c r="J79">
-        <v>2.2140343189239502</v>
+        <v>2.2372369766235352</v>
       </c>
       <c r="K79">
-        <v>43.848976135253913</v>
+        <v>35.316017150878913</v>
       </c>
       <c r="L79">
-        <v>149.9082336425781</v>
+        <v>137.7830505371094</v>
       </c>
       <c r="M79">
-        <v>157.86280822753909</v>
+        <v>149.81724548339841</v>
       </c>
       <c r="N79">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="O79">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="P79">
-        <v>1.9753273725509639</v>
+        <v>2.1964483261108398</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.3">
@@ -4835,49 +5039,49 @@
         <v>94</v>
       </c>
       <c r="B80">
-        <v>14.1</v>
+        <v>11</v>
       </c>
       <c r="C80">
-        <v>0.39720559120178223</v>
+        <v>0.3978022038936615</v>
       </c>
       <c r="D80">
-        <v>28.31387901306152</v>
+        <v>22.649517059326168</v>
       </c>
       <c r="E80">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F80">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G80">
-        <v>1.5203498336598571</v>
+        <v>1.3983758988558179</v>
       </c>
       <c r="H80">
-        <v>0.32156863808631903</v>
+        <v>0.29019609093666082</v>
       </c>
       <c r="I80">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="J80">
-        <v>2.2339644432067871</v>
+        <v>2.2526752948760991</v>
       </c>
       <c r="K80">
-        <v>36.657508850097663</v>
+        <v>34.692920684814453</v>
       </c>
       <c r="L80">
-        <v>141.99591064453119</v>
+        <v>150.99951171875</v>
       </c>
       <c r="M80">
-        <v>145.260009765625</v>
+        <v>144.75128173828119</v>
       </c>
       <c r="N80">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="O80">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="P80">
-        <v>2.1603293418884282</v>
+        <v>2.245625495910645</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.3">
@@ -4885,49 +5089,49 @@
         <v>95</v>
       </c>
       <c r="B81">
-        <v>15.7</v>
+        <v>14.3</v>
       </c>
       <c r="C81">
-        <v>0.40372669696807861</v>
+        <v>0.38057741522789001</v>
       </c>
       <c r="D81">
-        <v>25.960237503051761</v>
+        <v>22.732851028442379</v>
       </c>
       <c r="E81">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="F81">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="G81">
-        <v>1.458164351213175</v>
+        <v>1.394478237149424</v>
       </c>
       <c r="H81">
-        <v>0.3333333432674408</v>
+        <v>0.29411765933036799</v>
       </c>
       <c r="I81">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J81">
-        <v>1.866783499717712</v>
+        <v>1.6525038480758669</v>
       </c>
       <c r="K81">
-        <v>39.183685302734382</v>
+        <v>51.747940063476563</v>
       </c>
       <c r="L81">
-        <v>146.57997131347659</v>
+        <v>129.32633972167969</v>
       </c>
       <c r="M81">
-        <v>146.33161926269531</v>
+        <v>141.17193603515619</v>
       </c>
       <c r="N81">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="O81">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="P81">
-        <v>1.7682920694351201</v>
+        <v>1.5790388584136961</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
@@ -4935,49 +5139,49 @@
         <v>96</v>
       </c>
       <c r="B82">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="C82">
-        <v>0.39832285046577448</v>
+        <v>0.364705890417099</v>
       </c>
       <c r="D82">
-        <v>24.08180046081543</v>
+        <v>19.934982299804691</v>
       </c>
       <c r="E82">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="F82">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="G82">
-        <v>1.4125228870140529</v>
+        <v>1.314688172404983</v>
       </c>
       <c r="H82">
-        <v>0.3333333432674408</v>
+        <v>0.28235295414924622</v>
       </c>
       <c r="I82">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="J82">
-        <v>2.1067130565643311</v>
+        <v>2.2371211051940918</v>
       </c>
       <c r="K82">
-        <v>44.787300109863281</v>
+        <v>47.136295318603523</v>
       </c>
       <c r="L82">
-        <v>139.5755615234375</v>
+        <v>130.02070617675781</v>
       </c>
       <c r="M82">
-        <v>146.28221130371091</v>
+        <v>146.0174255371094</v>
       </c>
       <c r="N82">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="O82">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P82">
-        <v>2.0649490356445308</v>
+        <v>1.9229998588562009</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.3">
@@ -4985,49 +5189,49 @@
         <v>97</v>
       </c>
       <c r="B83">
-        <v>13.6</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="C83">
-        <v>0.4077448844909668</v>
+        <v>0.37352246046066279</v>
       </c>
       <c r="D83">
-        <v>27.309881210327148</v>
+        <v>19.465763092041019</v>
       </c>
       <c r="E83">
-        <v>186</v>
+        <v>141</v>
       </c>
       <c r="F83">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="G83">
-        <v>1.4684998160165641</v>
+        <v>1.349565392366378</v>
       </c>
       <c r="H83">
-        <v>0.35686275362968439</v>
+        <v>0.30588236451148992</v>
       </c>
       <c r="I83">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="J83">
-        <v>2.3577249050140381</v>
+        <v>2.354329109191895</v>
       </c>
       <c r="K83">
-        <v>38.945327758789063</v>
+        <v>39.659603118896477</v>
       </c>
       <c r="L83">
-        <v>146.65687561035159</v>
+        <v>113.44276428222661</v>
       </c>
       <c r="M83">
-        <v>152.46490478515619</v>
+        <v>129.06608581542969</v>
       </c>
       <c r="N83">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="O83">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="P83">
-        <v>2.1593103408813481</v>
+        <v>2.3888673782348628</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.3">
@@ -5035,49 +5239,49 @@
         <v>98</v>
       </c>
       <c r="B84">
-        <v>15.4</v>
+        <v>8.1</v>
       </c>
       <c r="C84">
-        <v>0.4309927225112915</v>
+        <v>0.3650793731212616</v>
       </c>
       <c r="D84">
-        <v>30.629327774047852</v>
+        <v>20.36036491394043</v>
       </c>
       <c r="E84">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="F84">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="G84">
-        <v>1.613227238970306</v>
+        <v>1.3314089595423311</v>
       </c>
       <c r="H84">
-        <v>0.40392157435417181</v>
+        <v>0.26274511218070978</v>
       </c>
       <c r="I84">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J84">
-        <v>2.2642586231231689</v>
+        <v>2.022480964660645</v>
       </c>
       <c r="K84">
-        <v>35.053558349609382</v>
+        <v>43.887538909912109</v>
       </c>
       <c r="L84">
-        <v>139.2833557128906</v>
+        <v>127.7581329345703</v>
       </c>
       <c r="M84">
-        <v>133.69749450683591</v>
+        <v>143.94425964355469</v>
       </c>
       <c r="N84">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O84">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="P84">
-        <v>2.1944301128387451</v>
+        <v>2.0928077697753911</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.3">
@@ -5085,49 +5289,49 @@
         <v>99</v>
       </c>
       <c r="B85">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="C85">
-        <v>0.40217390656471252</v>
+        <v>0.37820512056350708</v>
       </c>
       <c r="D85">
-        <v>27.657648086547852</v>
+        <v>22.322427749633789</v>
       </c>
       <c r="E85">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="F85">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="G85">
-        <v>1.501837667485576</v>
+        <v>1.3624942488181631</v>
       </c>
       <c r="H85">
         <v>0.32156863808631903</v>
       </c>
       <c r="I85">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J85">
-        <v>2.0546867847442631</v>
+        <v>1.906192421913147</v>
       </c>
       <c r="K85">
-        <v>36.779342651367188</v>
+        <v>50.254566192626953</v>
       </c>
       <c r="L85">
-        <v>145.32814025878909</v>
+        <v>135.60968017578119</v>
       </c>
       <c r="M85">
-        <v>144.77545166015619</v>
+        <v>148.91026306152341</v>
       </c>
       <c r="N85">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O85">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="P85">
-        <v>2.06242847442627</v>
+        <v>1.7139019966125491</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.3">
@@ -5135,49 +5339,49 @@
         <v>100</v>
       </c>
       <c r="B86">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
       <c r="C86">
-        <v>0.37119674682617188</v>
+        <v>0.37675350904464722</v>
       </c>
       <c r="D86">
-        <v>18.269975662231449</v>
+        <v>22.920490264892582</v>
       </c>
       <c r="E86">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="F86">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="G86">
-        <v>1.2723077201798501</v>
+        <v>1.4013666863472749</v>
       </c>
       <c r="H86">
-        <v>0.23529411852359769</v>
+        <v>0.28627452254295349</v>
       </c>
       <c r="I86">
         <v>192</v>
       </c>
       <c r="J86">
-        <v>2.2893285751342769</v>
+        <v>2.1641275882720952</v>
       </c>
       <c r="K86">
-        <v>31.927253723144531</v>
+        <v>44.030487060546882</v>
       </c>
       <c r="L86">
-        <v>150.75238037109381</v>
+        <v>128.0562744140625</v>
       </c>
       <c r="M86">
-        <v>158.65904235839841</v>
+        <v>142.07170104980469</v>
       </c>
       <c r="N86">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="O86">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="P86">
-        <v>2.0367121696472168</v>
+        <v>2.1998181343078609</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.3">
@@ -5185,49 +5389,49 @@
         <v>101</v>
       </c>
       <c r="B87">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="C87">
-        <v>0.4004376232624054</v>
+        <v>0.3888888955116272</v>
       </c>
       <c r="D87">
-        <v>23.049478530883789</v>
+        <v>25.984710693359379</v>
       </c>
       <c r="E87">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="F87">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="G87">
-        <v>1.3843463825330391</v>
+        <v>1.4501487759263429</v>
       </c>
       <c r="H87">
-        <v>0.30196079611778259</v>
+        <v>0.34117648005485529</v>
       </c>
       <c r="I87">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="J87">
-        <v>2.115591287612915</v>
+        <v>2.270864725112915</v>
       </c>
       <c r="K87">
-        <v>38.629871368408203</v>
+        <v>40.10882568359375</v>
       </c>
       <c r="L87">
-        <v>155.578125</v>
+        <v>131.09947204589841</v>
       </c>
       <c r="M87">
-        <v>152.97264099121091</v>
+        <v>147.77333068847659</v>
       </c>
       <c r="N87">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O87">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="P87">
-        <v>1.907040119171143</v>
+        <v>2.2199585437774658</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.3">
@@ -5235,49 +5439,49 @@
         <v>102</v>
       </c>
       <c r="B88">
-        <v>13.9</v>
+        <v>15.5</v>
       </c>
       <c r="C88">
-        <v>0.41067284345626831</v>
+        <v>0.38214287161827087</v>
       </c>
       <c r="D88">
-        <v>26.12821197509766</v>
+        <v>23.56021690368652</v>
       </c>
       <c r="E88">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F88">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="G88">
-        <v>1.4704355598155709</v>
+        <v>1.431357355404457</v>
       </c>
       <c r="H88">
-        <v>0.34117648005485529</v>
+        <v>0.29411765933036799</v>
       </c>
       <c r="I88">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="J88">
-        <v>3.0173766613006592</v>
+        <v>2.2983582019805908</v>
       </c>
       <c r="K88">
-        <v>32.034500122070313</v>
+        <v>38.723812103271477</v>
       </c>
       <c r="L88">
-        <v>141.99156188964841</v>
+        <v>126.3147430419922</v>
       </c>
       <c r="M88">
-        <v>144.68293762207031</v>
+        <v>138.7533874511719</v>
       </c>
       <c r="N88">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="O88">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="P88">
-        <v>2.816193580627441</v>
+        <v>2.2207381725311279</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.3">
@@ -5285,49 +5489,49 @@
         <v>103</v>
       </c>
       <c r="B89">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="C89">
-        <v>0.39045554399490362</v>
+        <v>0.37295082211494451</v>
       </c>
       <c r="D89">
-        <v>24.332571029663089</v>
+        <v>20.838933944702148</v>
       </c>
       <c r="E89">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="F89">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="G89">
-        <v>1.3988519982415859</v>
+        <v>1.324226381873534</v>
       </c>
       <c r="H89">
-        <v>0.29019609093666082</v>
+        <v>0.26274511218070978</v>
       </c>
       <c r="I89">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="J89">
-        <v>2.0024344921112061</v>
+        <v>2.1211552619934082</v>
       </c>
       <c r="K89">
-        <v>41.317085266113281</v>
+        <v>39.082614898681641</v>
       </c>
       <c r="L89">
-        <v>152.466796875</v>
+        <v>140.5149841308594</v>
       </c>
       <c r="M89">
-        <v>154.82867431640619</v>
+        <v>153.1911315917969</v>
       </c>
       <c r="N89">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="O89">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="P89">
-        <v>1.975751638412476</v>
+        <v>2.0715188980102539</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.3">
@@ -5335,49 +5539,49 @@
         <v>104</v>
       </c>
       <c r="B90">
-        <v>14.7</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="C90">
-        <v>0.41689372062683111</v>
+        <v>0.36530610918998718</v>
       </c>
       <c r="D90">
-        <v>31.705753326416019</v>
+        <v>17.841976165771481</v>
       </c>
       <c r="E90">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="F90">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="G90">
-        <v>1.650299166989438</v>
+        <v>1.2396015595698591</v>
       </c>
       <c r="H90">
-        <v>0.37254902720451349</v>
+        <v>0.25882354378700262</v>
       </c>
       <c r="I90">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="J90">
-        <v>2.33311939239502</v>
+        <v>2.4223465919494629</v>
       </c>
       <c r="K90">
-        <v>32.701877593994141</v>
+        <v>44.326320648193359</v>
       </c>
       <c r="L90">
-        <v>136.3662109375</v>
+        <v>140.10432434082031</v>
       </c>
       <c r="M90">
-        <v>134.03715515136719</v>
+        <v>158.73414611816409</v>
       </c>
       <c r="N90">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="O90">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="P90">
-        <v>2.2482049465179439</v>
+        <v>1.9775655269622801</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
@@ -5385,49 +5589,49 @@
         <v>105</v>
       </c>
       <c r="B91">
-        <v>15.4</v>
+        <v>11.8</v>
       </c>
       <c r="C91">
-        <v>0.40446650981903082</v>
+        <v>0.40993788838386541</v>
       </c>
       <c r="D91">
-        <v>28.469297409057621</v>
+        <v>28.452554702758789</v>
       </c>
       <c r="E91">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F91">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="G91">
-        <v>1.568115973928732</v>
+        <v>1.5104398704420099</v>
       </c>
       <c r="H91">
-        <v>0.3333333432674408</v>
+        <v>0.32941177487373352</v>
       </c>
       <c r="I91">
         <v>189</v>
       </c>
       <c r="J91">
-        <v>2.1085994243621831</v>
+        <v>2.27857518196106</v>
       </c>
       <c r="K91">
-        <v>40.986747741699219</v>
+        <v>29.225004196166989</v>
       </c>
       <c r="L91">
-        <v>134.51336669921881</v>
+        <v>152.2423095703125</v>
       </c>
       <c r="M91">
-        <v>132.7209167480469</v>
+        <v>148.02131652832031</v>
       </c>
       <c r="N91">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O91">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="P91">
-        <v>2.0384092330932622</v>
+        <v>2.1961650848388672</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
@@ -5435,49 +5639,49 @@
         <v>106</v>
       </c>
       <c r="B92">
-        <v>14.9</v>
+        <v>10.3</v>
       </c>
       <c r="C92">
-        <v>0.43023255467414862</v>
+        <v>0.3516746461391449</v>
       </c>
       <c r="D92">
-        <v>29.062643051147461</v>
+        <v>16.66091156005859</v>
       </c>
       <c r="E92">
+        <v>179</v>
+      </c>
+      <c r="F92">
+        <v>117</v>
+      </c>
+      <c r="G92">
+        <v>1.2056536423191271</v>
+      </c>
+      <c r="H92">
+        <v>0.21176470816135409</v>
+      </c>
+      <c r="I92">
         <v>194</v>
       </c>
-      <c r="F92">
-        <v>143</v>
-      </c>
-      <c r="G92">
-        <v>1.600290464969607</v>
-      </c>
-      <c r="H92">
-        <v>0.37254902720451349</v>
-      </c>
-      <c r="I92">
-        <v>175</v>
-      </c>
       <c r="J92">
-        <v>2.359338760375977</v>
+        <v>2.4716224670410161</v>
       </c>
       <c r="K92">
-        <v>28.5696907043457</v>
+        <v>41.120296478271477</v>
       </c>
       <c r="L92">
-        <v>138.5892639160156</v>
+        <v>148.57505798339841</v>
       </c>
       <c r="M92">
-        <v>127.7242050170898</v>
+        <v>167.40936279296881</v>
       </c>
       <c r="N92">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="O92">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="P92">
-        <v>2.1780951023101811</v>
+        <v>2.047423362731934</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
@@ -5485,49 +5689,49 @@
         <v>107</v>
       </c>
       <c r="B93">
-        <v>14.1</v>
+        <v>12.5</v>
       </c>
       <c r="C93">
-        <v>0.37179487943649292</v>
+        <v>0.38053098320960999</v>
       </c>
       <c r="D93">
-        <v>18.428304672241211</v>
+        <v>24.42723274230957</v>
       </c>
       <c r="E93">
+        <v>179</v>
+      </c>
+      <c r="F93">
+        <v>140</v>
+      </c>
+      <c r="G93">
+        <v>1.386572588262265</v>
+      </c>
+      <c r="H93">
+        <v>0.28627452254295349</v>
+      </c>
+      <c r="I93">
+        <v>200</v>
+      </c>
+      <c r="J93">
+        <v>2.3029394149780269</v>
+      </c>
+      <c r="K93">
+        <v>38.016338348388672</v>
+      </c>
+      <c r="L93">
+        <v>144.98872375488281</v>
+      </c>
+      <c r="M93">
+        <v>158.59864807128909</v>
+      </c>
+      <c r="N93">
+        <v>99</v>
+      </c>
+      <c r="O93">
         <v>193</v>
       </c>
-      <c r="F93">
-        <v>117</v>
-      </c>
-      <c r="G93">
-        <v>1.262021813270181</v>
-      </c>
-      <c r="H93">
-        <v>0.24705882370471949</v>
-      </c>
-      <c r="I93">
-        <v>202</v>
-      </c>
-      <c r="J93">
-        <v>2.7597122192382808</v>
-      </c>
-      <c r="K93">
-        <v>35.961315155029297</v>
-      </c>
-      <c r="L93">
-        <v>155.97340393066409</v>
-      </c>
-      <c r="M93">
-        <v>165.37214660644531</v>
-      </c>
-      <c r="N93">
-        <v>109</v>
-      </c>
-      <c r="O93">
-        <v>195</v>
-      </c>
       <c r="P93">
-        <v>2.4143316745758061</v>
+        <v>2.1619453430175781</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
@@ -5535,49 +5739,49 @@
         <v>108</v>
       </c>
       <c r="B94">
-        <v>14.1</v>
+        <v>10.6</v>
       </c>
       <c r="C94">
-        <v>0.40900194644927979</v>
+        <v>0.37861916422843928</v>
       </c>
       <c r="D94">
-        <v>29.26578330993652</v>
+        <v>20.7618293762207</v>
       </c>
       <c r="E94">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="F94">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="G94">
-        <v>1.5003082551171381</v>
+        <v>1.3547242857078721</v>
       </c>
       <c r="H94">
-        <v>0.32549020648002619</v>
+        <v>0.29411765933036799</v>
       </c>
       <c r="I94">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="J94">
-        <v>2.2975947856903081</v>
+        <v>3.0072672367095952</v>
       </c>
       <c r="K94">
-        <v>32.328346252441413</v>
+        <v>40.431167602539063</v>
       </c>
       <c r="L94">
-        <v>161.1357116699219</v>
+        <v>124.57904052734381</v>
       </c>
       <c r="M94">
-        <v>156.69476318359381</v>
+        <v>138.89436340332031</v>
       </c>
       <c r="N94">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="O94">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="P94">
-        <v>2.270307302474976</v>
+        <v>3.0216817855834961</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
@@ -5585,49 +5789,49 @@
         <v>109</v>
       </c>
       <c r="B95">
-        <v>16.100000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="C95">
-        <v>0.36363637447357178</v>
+        <v>0.3571428656578064</v>
       </c>
       <c r="D95">
-        <v>21.4205436706543</v>
+        <v>19.10154914855957</v>
       </c>
       <c r="E95">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="F95">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="G95">
-        <v>1.2958273971516669</v>
+        <v>1.2581697917869701</v>
       </c>
       <c r="H95">
-        <v>0.21960784494876859</v>
+        <v>0.23921568691730499</v>
       </c>
       <c r="I95">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="J95">
-        <v>2.1911964416503911</v>
+        <v>2.0087966918945308</v>
       </c>
       <c r="K95">
-        <v>39.862201690673828</v>
+        <v>43.991649627685547</v>
       </c>
       <c r="L95">
-        <v>164.00315856933591</v>
+        <v>143.39955139160159</v>
       </c>
       <c r="M95">
-        <v>174.9908752441406</v>
+        <v>162.87986755371091</v>
       </c>
       <c r="N95">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="O95">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="P95">
-        <v>2.104111909866333</v>
+        <v>1.730189204216003</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
@@ -5635,49 +5839,49 @@
         <v>110</v>
       </c>
       <c r="B96">
-        <v>15.1</v>
+        <v>10.8</v>
       </c>
       <c r="C96">
-        <v>0.40122199058532709</v>
+        <v>0.36468330025672913</v>
       </c>
       <c r="D96">
-        <v>23.419643402099609</v>
+        <v>18.45468711853027</v>
       </c>
       <c r="E96">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="F96">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="G96">
-        <v>1.3990718861779019</v>
+        <v>1.268234076931406</v>
       </c>
       <c r="H96">
-        <v>0.30588236451148992</v>
+        <v>0.2431372553110123</v>
       </c>
       <c r="I96">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J96">
-        <v>2.4576847553253169</v>
+        <v>2.3330368995666499</v>
       </c>
       <c r="K96">
-        <v>39.395484924316413</v>
+        <v>43.653854370117188</v>
       </c>
       <c r="L96">
-        <v>150.6950988769531</v>
+        <v>136.9246520996094</v>
       </c>
       <c r="M96">
-        <v>150.1626892089844</v>
+        <v>152.85057067871091</v>
       </c>
       <c r="N96">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O96">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P96">
-        <v>2.261107444763184</v>
+        <v>2.280230045318604</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.3">
@@ -5685,49 +5889,49 @@
         <v>111</v>
       </c>
       <c r="B97">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="C97">
-        <v>0.37109375</v>
+        <v>0.35805085301399231</v>
       </c>
       <c r="D97">
-        <v>22.126142501831051</v>
+        <v>20.924404144287109</v>
       </c>
       <c r="E97">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F97">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="G97">
-        <v>1.3226036386288</v>
+        <v>1.2909022343545711</v>
       </c>
       <c r="H97">
-        <v>0.24705882370471949</v>
+        <v>0.29803922772407532</v>
       </c>
       <c r="I97">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="J97">
-        <v>3.8973085880279541</v>
+        <v>2.1241226196289058</v>
       </c>
       <c r="K97">
-        <v>21.66053581237793</v>
+        <v>36.862617492675781</v>
       </c>
       <c r="L97">
-        <v>154.4453125</v>
+        <v>140.88172912597659</v>
       </c>
       <c r="M97">
-        <v>168.3892517089844</v>
+        <v>161.71232604980469</v>
       </c>
       <c r="N97">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="O97">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="P97">
-        <v>3.151129007339478</v>
+        <v>1.9907535314559941</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.3">
@@ -5735,49 +5939,49 @@
         <v>112</v>
       </c>
       <c r="B98">
-        <v>15.3</v>
+        <v>9.9</v>
       </c>
       <c r="C98">
-        <v>0.39851483702659612</v>
+        <v>0.36032387614250178</v>
       </c>
       <c r="D98">
-        <v>22.846548080444339</v>
+        <v>18.491487503051761</v>
       </c>
       <c r="E98">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="F98">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="G98">
-        <v>1.389383545194862</v>
+        <v>1.252952937792446</v>
       </c>
       <c r="H98">
-        <v>0.31372550129890442</v>
+        <v>0.27843138575553888</v>
       </c>
       <c r="I98">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J98">
-        <v>2.6938433647155762</v>
+        <v>2.2959132194519039</v>
       </c>
       <c r="K98">
-        <v>42.098976135253913</v>
+        <v>44.647861480712891</v>
       </c>
       <c r="L98">
-        <v>147.86381530761719</v>
+        <v>133.8527526855469</v>
       </c>
       <c r="M98">
-        <v>149.15946960449219</v>
+        <v>154.0249938964844</v>
       </c>
       <c r="N98">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O98">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="P98">
-        <v>2.1817536354064941</v>
+        <v>1.980048775672913</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.3">
@@ -5785,49 +5989,49 @@
         <v>113</v>
       </c>
       <c r="B99">
-        <v>13.9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="C99">
-        <v>0.40286299586296082</v>
+        <v>0.35130718350410461</v>
       </c>
       <c r="D99">
-        <v>28.446718215942379</v>
+        <v>16.076980590820309</v>
       </c>
       <c r="E99">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F99">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="G99">
-        <v>1.5025420876922311</v>
+        <v>1.181922556698489</v>
       </c>
       <c r="H99">
-        <v>0.33725491166114813</v>
+        <v>0.17647059261798859</v>
       </c>
       <c r="I99">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J99">
-        <v>2.163744211196899</v>
+        <v>5.4167938232421884</v>
       </c>
       <c r="K99">
-        <v>37.857139587402337</v>
+        <v>32.736007690429688</v>
       </c>
       <c r="L99">
-        <v>149.86033630371091</v>
+        <v>173.03028869628909</v>
       </c>
       <c r="M99">
-        <v>150.47395324707031</v>
+        <v>190.27705383300781</v>
       </c>
       <c r="N99">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="O99">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="P99">
-        <v>2.0751328468322749</v>
+        <v>4.2524561882019043</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.3">
@@ -5835,49 +6039,49 @@
         <v>114</v>
       </c>
       <c r="B100">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="C100">
-        <v>0.41299790143966669</v>
+        <v>0.38276553153991699</v>
       </c>
       <c r="D100">
-        <v>28.098196029663089</v>
+        <v>25.57353591918945</v>
       </c>
       <c r="E100">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="F100">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="G100">
-        <v>1.501295801388431</v>
+        <v>1.426323619253975</v>
       </c>
       <c r="H100">
-        <v>0.3490196168422699</v>
+        <v>0.32549020648002619</v>
       </c>
       <c r="I100">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="J100">
-        <v>2.1504542827606201</v>
+        <v>2.8727202415466309</v>
       </c>
       <c r="K100">
-        <v>37.744338989257813</v>
+        <v>37.458499908447273</v>
       </c>
       <c r="L100">
-        <v>151.2465515136719</v>
+        <v>138.29266357421881</v>
       </c>
       <c r="M100">
-        <v>148.4222106933594</v>
+        <v>153.78973388671881</v>
       </c>
       <c r="N100">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="O100">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="P100">
-        <v>2.070000171661377</v>
+        <v>2.6129248142242432</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.3">
@@ -5885,49 +6089,49 @@
         <v>115</v>
       </c>
       <c r="B101">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="C101">
-        <v>0.40709811449050898</v>
+        <v>0.36137071251869202</v>
       </c>
       <c r="D101">
-        <v>29.878969192504879</v>
+        <v>20.032926559448239</v>
       </c>
       <c r="E101">
+        <v>148</v>
+      </c>
+      <c r="F101">
+        <v>98</v>
+      </c>
+      <c r="G101">
+        <v>1.315960954517629</v>
+      </c>
+      <c r="H101">
+        <v>0.27058824896812439</v>
+      </c>
+      <c r="I101">
+        <v>198</v>
+      </c>
+      <c r="J101">
+        <v>2.127010822296143</v>
+      </c>
+      <c r="K101">
+        <v>44.574287414550781</v>
+      </c>
+      <c r="L101">
+        <v>126.0551071166992</v>
+      </c>
+      <c r="M101">
+        <v>144.0640563964844</v>
+      </c>
+      <c r="N101">
+        <v>84</v>
+      </c>
+      <c r="O101">
         <v>186</v>
       </c>
-      <c r="F101">
-        <v>161</v>
-      </c>
-      <c r="G101">
-        <v>1.561008743712569</v>
-      </c>
-      <c r="H101">
-        <v>0.35294118523597717</v>
-      </c>
-      <c r="I101">
-        <v>176</v>
-      </c>
-      <c r="J101">
-        <v>3.1164038181304932</v>
-      </c>
-      <c r="K101">
-        <v>26.981931686401371</v>
-      </c>
-      <c r="L101">
-        <v>140.36683654785159</v>
-      </c>
-      <c r="M101">
-        <v>145.02928161621091</v>
-      </c>
-      <c r="N101">
-        <v>101</v>
-      </c>
-      <c r="O101">
-        <v>168</v>
-      </c>
       <c r="P101">
-        <v>3.1335291862487789</v>
+        <v>2.1883630752563481</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.3">
@@ -5935,49 +6139,49 @@
         <v>116</v>
       </c>
       <c r="B102">
-        <v>15.3</v>
+        <v>11</v>
       </c>
       <c r="C102">
-        <v>0.39325842261314392</v>
+        <v>0.37037035822868353</v>
       </c>
       <c r="D102">
-        <v>25.51174354553223</v>
+        <v>18.94943809509277</v>
       </c>
       <c r="E102">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F102">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="G102">
-        <v>1.445151489156105</v>
+        <v>1.278400620001662</v>
       </c>
       <c r="H102">
-        <v>0.29411765933036799</v>
+        <v>0.23921568691730499</v>
       </c>
       <c r="I102">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J102">
-        <v>1.986564040184021</v>
+        <v>2.1344208717346191</v>
       </c>
       <c r="K102">
-        <v>42.914539337158203</v>
+        <v>37.956794738769531</v>
       </c>
       <c r="L102">
-        <v>150.8766784667969</v>
+        <v>152.48497009277341</v>
       </c>
       <c r="M102">
-        <v>147.53900146484381</v>
+        <v>161.77861022949219</v>
       </c>
       <c r="N102">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="O102">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P102">
-        <v>1.8946355581283569</v>
+        <v>2.083043098449707</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.3">
@@ -5985,49 +6189,49 @@
         <v>117</v>
       </c>
       <c r="B103">
-        <v>16.899999999999999</v>
+        <v>14</v>
       </c>
       <c r="C103">
-        <v>0.38955822587013239</v>
+        <v>0.38732394576072687</v>
       </c>
       <c r="D103">
-        <v>25.536233901977539</v>
+        <v>22.441291809082031</v>
       </c>
       <c r="E103">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="F103">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="G103">
-        <v>1.438157966543113</v>
+        <v>1.4175025312224581</v>
       </c>
       <c r="H103">
-        <v>0.29019609093666082</v>
+        <v>0.33725491166114813</v>
       </c>
       <c r="I103">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="J103">
-        <v>2.5403785705566411</v>
+        <v>2.6876552104949951</v>
       </c>
       <c r="K103">
-        <v>43.481307983398438</v>
+        <v>38.773353576660163</v>
       </c>
       <c r="L103">
-        <v>147.88011169433591</v>
+        <v>123.0794143676758</v>
       </c>
       <c r="M103">
-        <v>151.2971496582031</v>
+        <v>133.9936218261719</v>
       </c>
       <c r="N103">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="O103">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="P103">
-        <v>2.0240767002105708</v>
+        <v>2.686151266098022</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
@@ -6035,49 +6239,49 @@
         <v>118</v>
       </c>
       <c r="B104">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="C104">
-        <v>0.3844660222530365</v>
+        <v>0.37413394451141357</v>
       </c>
       <c r="D104">
-        <v>22.450162887573239</v>
+        <v>20.62894439697266</v>
       </c>
       <c r="E104">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="F104">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="G104">
-        <v>1.3594238878082241</v>
+        <v>1.375324891708245</v>
       </c>
       <c r="H104">
-        <v>0.26666668057441711</v>
+        <v>0.29411765933036799</v>
       </c>
       <c r="I104">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="J104">
-        <v>2.1066691875457759</v>
+        <v>2.783852100372314</v>
       </c>
       <c r="K104">
-        <v>40.623622894287109</v>
+        <v>40.438583374023438</v>
       </c>
       <c r="L104">
-        <v>155.24177551269531</v>
+        <v>116.80177307128911</v>
       </c>
       <c r="M104">
-        <v>157.7576599121094</v>
+        <v>130.66021728515619</v>
       </c>
       <c r="N104">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="O104">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="P104">
-        <v>2.0218064785003662</v>
+        <v>3.0753154754638672</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.3">
@@ -6085,49 +6289,49 @@
         <v>119</v>
       </c>
       <c r="B105">
-        <v>13.5</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="C105">
-        <v>0.40408164262771612</v>
+        <v>0.36338797211647028</v>
       </c>
       <c r="D105">
-        <v>24.64246940612793</v>
+        <v>20.517486572265621</v>
       </c>
       <c r="E105">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="F105">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="G105">
-        <v>1.408326288044482</v>
+        <v>1.3381455860920699</v>
       </c>
       <c r="H105">
-        <v>0.30980393290519709</v>
+        <v>0.30588236451148992</v>
       </c>
       <c r="I105">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="J105">
-        <v>2.2150595188140869</v>
+        <v>2.1981973648071289</v>
       </c>
       <c r="K105">
-        <v>33.741451263427727</v>
+        <v>48.521930694580078</v>
       </c>
       <c r="L105">
-        <v>159.2691955566406</v>
+        <v>119.5120086669922</v>
       </c>
       <c r="M105">
-        <v>155.98907470703119</v>
+        <v>139.0904846191406</v>
       </c>
       <c r="N105">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="O105">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="P105">
-        <v>2.072587251663208</v>
+        <v>2.1396803855896001</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.3">
@@ -6135,49 +6339,49 @@
         <v>120</v>
       </c>
       <c r="B106">
-        <v>15</v>
+        <v>10.6</v>
       </c>
       <c r="C106">
-        <v>0.41079813241958618</v>
+        <v>0.35668790340423578</v>
       </c>
       <c r="D106">
-        <v>27.889167785644531</v>
+        <v>17.724002838134769</v>
       </c>
       <c r="E106">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="F106">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="G106">
-        <v>1.526324962768459</v>
+        <v>1.2500123667012331</v>
       </c>
       <c r="H106">
-        <v>0.34117648005485529</v>
+        <v>0.27450981736183172</v>
       </c>
       <c r="I106">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="J106">
-        <v>2.0029277801513672</v>
+        <v>2.066900253295898</v>
       </c>
       <c r="K106">
-        <v>36.829135894775391</v>
+        <v>45.613964080810547</v>
       </c>
       <c r="L106">
-        <v>143.01554870605469</v>
+        <v>125.63283538818359</v>
       </c>
       <c r="M106">
-        <v>139.43443298339841</v>
+        <v>146.17848205566409</v>
       </c>
       <c r="N106">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="O106">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="P106">
-        <v>2.068879365921021</v>
+        <v>1.9376316070556641</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.3">
@@ -6185,49 +6389,49 @@
         <v>121</v>
       </c>
       <c r="B107">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="C107">
-        <v>0.40890687704086298</v>
+        <v>0.35845214128494263</v>
       </c>
       <c r="D107">
-        <v>27.528945922851559</v>
+        <v>19.122526168823239</v>
       </c>
       <c r="E107">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F107">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="G107">
-        <v>1.4927820566063099</v>
+        <v>1.296856521929409</v>
       </c>
       <c r="H107">
-        <v>0.34117648005485529</v>
+        <v>0.28235295414924622</v>
       </c>
       <c r="I107">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J107">
-        <v>1.9905633926391599</v>
+        <v>2.1764733791351318</v>
       </c>
       <c r="K107">
-        <v>35.004123687744141</v>
+        <v>46.27435302734375</v>
       </c>
       <c r="L107">
-        <v>145.70661926269531</v>
+        <v>127.9107360839844</v>
       </c>
       <c r="M107">
-        <v>147.19142150878909</v>
+        <v>145.2304992675781</v>
       </c>
       <c r="N107">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="O107">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="P107">
-        <v>1.9841358661651609</v>
+        <v>1.981735467910767</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.3">
@@ -6235,49 +6439,49 @@
         <v>122</v>
       </c>
       <c r="B108">
-        <v>15</v>
+        <v>12.7</v>
       </c>
       <c r="C108">
-        <v>0.36559140682220459</v>
+        <v>0.3681214451789856</v>
       </c>
       <c r="D108">
-        <v>18.914913177490231</v>
+        <v>22.401418685913089</v>
       </c>
       <c r="E108">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F108">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="G108">
-        <v>1.256006313636993</v>
+        <v>1.3280624013088971</v>
       </c>
       <c r="H108">
-        <v>0.21176470816135409</v>
+        <v>0.25490197539329529</v>
       </c>
       <c r="I108">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="J108">
-        <v>2.7819609642028809</v>
+        <v>2.9512135982513432</v>
       </c>
       <c r="K108">
-        <v>28.985956192016602</v>
+        <v>39.024158477783203</v>
       </c>
       <c r="L108">
-        <v>163.80888366699219</v>
+        <v>150.44154357910159</v>
       </c>
       <c r="M108">
-        <v>174.9359130859375</v>
+        <v>166.34747314453119</v>
       </c>
       <c r="N108">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="O108">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P108">
-        <v>2.6076779365539551</v>
+        <v>2.2961440086364751</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.3">
@@ -6285,49 +6489,49 @@
         <v>123</v>
       </c>
       <c r="B109">
-        <v>15.6</v>
+        <v>12.3</v>
       </c>
       <c r="C109">
-        <v>0.37940379977226257</v>
+        <v>0.35867446660995478</v>
       </c>
       <c r="D109">
-        <v>25.547161102294918</v>
+        <v>17.183364868164059</v>
       </c>
       <c r="E109">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="F109">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="G109">
-        <v>1.380156379783124</v>
+        <v>1.221722323050886</v>
       </c>
       <c r="H109">
-        <v>0.26666668057441711</v>
+        <v>0.22745098173618319</v>
       </c>
       <c r="I109">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="J109">
-        <v>2.8014175891876221</v>
+        <v>2.3618893623352051</v>
       </c>
       <c r="K109">
-        <v>36.849796295166023</v>
+        <v>40.623336791992188</v>
       </c>
       <c r="L109">
-        <v>165.58738708496091</v>
+        <v>147.5250549316406</v>
       </c>
       <c r="M109">
-        <v>174.14208984375</v>
+        <v>165.23576354980469</v>
       </c>
       <c r="N109">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="O109">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="P109">
-        <v>2.355512380599976</v>
+        <v>2.1062383651733398</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.3">
@@ -6335,49 +6539,49 @@
         <v>124</v>
       </c>
       <c r="B110">
-        <v>15</v>
+        <v>9.1</v>
       </c>
       <c r="C110">
-        <v>0.38518518209457397</v>
+        <v>0.37061402201652532</v>
       </c>
       <c r="D110">
-        <v>24.069316864013668</v>
+        <v>19.748922348022461</v>
       </c>
       <c r="E110">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="F110">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G110">
-        <v>1.381247139825583</v>
+        <v>1.2847488914164209</v>
       </c>
       <c r="H110">
-        <v>0.27843138575553888</v>
+        <v>0.23137255012989039</v>
       </c>
       <c r="I110">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="J110">
-        <v>3.3420710563659668</v>
+        <v>3.463811874389648</v>
       </c>
       <c r="K110">
-        <v>35.554473876953118</v>
+        <v>24.368612289428711</v>
       </c>
       <c r="L110">
-        <v>157.02900695800781</v>
+        <v>153.0386657714844</v>
       </c>
       <c r="M110">
-        <v>162.23973083496091</v>
+        <v>165.61241149902341</v>
       </c>
       <c r="N110">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="O110">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="P110">
-        <v>2.716183185577393</v>
+        <v>3.3418676853179932</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
@@ -6385,49 +6589,49 @@
         <v>125</v>
       </c>
       <c r="B111">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="C111">
-        <v>0.38533833622932429</v>
+        <v>0.371702641248703</v>
       </c>
       <c r="D111">
-        <v>24.069869995117191</v>
+        <v>21.469354629516602</v>
       </c>
       <c r="E111">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="F111">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="G111">
-        <v>1.3799206585913439</v>
+        <v>1.3542716371360719</v>
       </c>
       <c r="H111">
-        <v>0.27843138575553888</v>
+        <v>0.29411765933036799</v>
       </c>
       <c r="I111">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="J111">
-        <v>2.7331511974334721</v>
+        <v>2.1437654495239258</v>
       </c>
       <c r="K111">
-        <v>39.436111450195313</v>
+        <v>39.788242340087891</v>
       </c>
       <c r="L111">
-        <v>157.39985656738281</v>
+        <v>128.44325256347659</v>
       </c>
       <c r="M111">
-        <v>162.44647216796881</v>
+        <v>144.14576721191409</v>
       </c>
       <c r="N111">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O111">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="P111">
-        <v>2.234538078308105</v>
+        <v>1.940875649452209</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.3">
@@ -6435,49 +6639,49 @@
         <v>126</v>
       </c>
       <c r="B112">
-        <v>14.9</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="C112">
-        <v>0.38208955526351929</v>
+        <v>0.36217305064201349</v>
       </c>
       <c r="D112">
-        <v>21.899881362915039</v>
+        <v>17.311540603637699</v>
       </c>
       <c r="E112">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="F112">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="G112">
-        <v>1.3322824644967779</v>
+        <v>1.2351988400358249</v>
       </c>
       <c r="H112">
-        <v>0.26666668057441711</v>
+        <v>0.2431372553110123</v>
       </c>
       <c r="I112">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="J112">
-        <v>2.224197626113892</v>
+        <v>2.5956027507781978</v>
       </c>
       <c r="K112">
-        <v>37.446193695068359</v>
+        <v>43.030399322509773</v>
       </c>
       <c r="L112">
-        <v>158.99273681640619</v>
+        <v>142.01402282714841</v>
       </c>
       <c r="M112">
-        <v>164.39830017089841</v>
+        <v>158.9377136230469</v>
       </c>
       <c r="N112">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="O112">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P112">
-        <v>2.091837882995605</v>
+        <v>2.231959342956543</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.3">
@@ -6485,49 +6689,49 @@
         <v>127</v>
       </c>
       <c r="B113">
-        <v>17.399999999999999</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="C113">
-        <v>0.39457201957702642</v>
+        <v>0.35836178064346308</v>
       </c>
       <c r="D113">
-        <v>28.334358215332031</v>
+        <v>16.692262649536129</v>
       </c>
       <c r="E113">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F113">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G113">
-        <v>1.4827921705859091</v>
+        <v>1.205726424101178</v>
       </c>
       <c r="H113">
-        <v>0.31764706969261169</v>
+        <v>0.18431372940540311</v>
       </c>
       <c r="I113">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="J113">
-        <v>2.6998238563537602</v>
+        <v>3.2205543518066411</v>
       </c>
       <c r="K113">
-        <v>30.4770622253418</v>
+        <v>29.026775360107418</v>
       </c>
       <c r="L113">
-        <v>150.41375732421881</v>
+        <v>170.5085754394531</v>
       </c>
       <c r="M113">
-        <v>156.4085998535156</v>
+        <v>183.42027282714841</v>
       </c>
       <c r="N113">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="O113">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="P113">
-        <v>2.4527263641357422</v>
+        <v>2.889278888702393</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.3">
@@ -6535,49 +6739,49 @@
         <v>128</v>
       </c>
       <c r="B114">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="C114">
-        <v>0.41588786244392401</v>
+        <v>0.42970821261405939</v>
       </c>
       <c r="D114">
-        <v>29.755178451538089</v>
+        <v>31.930524826049801</v>
       </c>
       <c r="E114">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F114">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="G114">
-        <v>1.584496583423364</v>
+        <v>1.6116149563817701</v>
       </c>
       <c r="H114">
-        <v>0.3803921639919281</v>
+        <v>0.40392157435417181</v>
       </c>
       <c r="I114">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J114">
-        <v>2.3581175804138179</v>
+        <v>2.3849482536315918</v>
       </c>
       <c r="K114">
-        <v>34.216083526611328</v>
+        <v>33.672168731689453</v>
       </c>
       <c r="L114">
-        <v>137.11302185058591</v>
+        <v>143.1998291015625</v>
       </c>
       <c r="M114">
-        <v>136.5146179199219</v>
+        <v>143.0824279785156</v>
       </c>
       <c r="N114">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="O114">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="P114">
-        <v>2.417370080947876</v>
+        <v>2.3251838684082031</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.3">
@@ -6585,49 +6789,49 @@
         <v>129</v>
       </c>
       <c r="B115">
-        <v>15.9</v>
+        <v>8.5</v>
       </c>
       <c r="C115">
-        <v>0.38530066609382629</v>
+        <v>0.37931033968925482</v>
       </c>
       <c r="D115">
-        <v>28.70645904541016</v>
+        <v>19.866083145141602</v>
       </c>
       <c r="E115">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="F115">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="G115">
-        <v>1.4643043029012319</v>
+        <v>1.371438829736727</v>
       </c>
       <c r="H115">
-        <v>0.30196079611778259</v>
+        <v>0.29019609093666082</v>
       </c>
       <c r="I115">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="J115">
-        <v>2.9558181762695308</v>
+        <v>2.7524211406707759</v>
       </c>
       <c r="K115">
-        <v>31.891448974609379</v>
+        <v>34.647747039794922</v>
       </c>
       <c r="L115">
-        <v>153.87469482421881</v>
+        <v>116.6812057495117</v>
       </c>
       <c r="M115">
-        <v>164.60707092285159</v>
+        <v>128.4617004394531</v>
       </c>
       <c r="N115">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="O115">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="P115">
-        <v>2.39207935333252</v>
+        <v>3.006445169448853</v>
       </c>
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.3">
@@ -6635,49 +6839,49 @@
         <v>130</v>
       </c>
       <c r="B116">
-        <v>16.2</v>
+        <v>10.3</v>
       </c>
       <c r="C116">
-        <v>0.38223937153816218</v>
+        <v>0.35147392749786383</v>
       </c>
       <c r="D116">
-        <v>25.392948150634769</v>
+        <v>16.3316764831543</v>
       </c>
       <c r="E116">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="F116">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="G116">
-        <v>1.387678089852217</v>
+        <v>1.199029787920912</v>
       </c>
       <c r="H116">
-        <v>0.29019609093666082</v>
+        <v>0.22352941334247589</v>
       </c>
       <c r="I116">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J116">
-        <v>2.3393592834472661</v>
+        <v>2.8226394653320308</v>
       </c>
       <c r="K116">
-        <v>33.140361785888672</v>
+        <v>41.058666229248047</v>
       </c>
       <c r="L116">
-        <v>154.14787292480469</v>
+        <v>147.19429016113281</v>
       </c>
       <c r="M116">
-        <v>166.75868225097659</v>
+        <v>166.943603515625</v>
       </c>
       <c r="N116">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="O116">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="P116">
-        <v>2.3512759208679199</v>
+        <v>2.239951610565186</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.3">
@@ -6685,49 +6889,49 @@
         <v>131</v>
       </c>
       <c r="B117">
-        <v>15.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="C117">
-        <v>0.38386309146881098</v>
+        <v>0.43781095743179321</v>
       </c>
       <c r="D117">
-        <v>26.608266830444339</v>
+        <v>25.704999923706051</v>
       </c>
       <c r="E117">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F117">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="G117">
-        <v>1.457845228402193</v>
+        <v>1.5599101573881951</v>
       </c>
       <c r="H117">
-        <v>0.29019609093666082</v>
+        <v>0.38823530077934271</v>
       </c>
       <c r="I117">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="J117">
-        <v>3.20001220703125</v>
+        <v>2.173568487167358</v>
       </c>
       <c r="K117">
-        <v>28.804193496704102</v>
+        <v>41.334430694580078</v>
       </c>
       <c r="L117">
-        <v>142.86027526855469</v>
+        <v>125.5594100952148</v>
       </c>
       <c r="M117">
-        <v>152.23497009277341</v>
+        <v>118.2695236206055</v>
       </c>
       <c r="N117">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="O117">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="P117">
-        <v>2.8189558982849121</v>
+        <v>2.0658121109008789</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.3">
@@ -6735,49 +6939,49 @@
         <v>132</v>
       </c>
       <c r="B118">
-        <v>14.1</v>
+        <v>10.5</v>
       </c>
       <c r="C118">
-        <v>0.38311687111854548</v>
+        <v>0.35333332419395452</v>
       </c>
       <c r="D118">
-        <v>23.241048812866211</v>
+        <v>17.629751205444339</v>
       </c>
       <c r="E118">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="F118">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="G118">
-        <v>1.349612305185649</v>
+        <v>1.2297009374834149</v>
       </c>
       <c r="H118">
-        <v>0.26274511218070978</v>
+        <v>0.25490197539329529</v>
       </c>
       <c r="I118">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="J118">
-        <v>2.894633531570435</v>
+        <v>2.2651669979095459</v>
       </c>
       <c r="K118">
-        <v>34.527275085449219</v>
+        <v>43.316215515136719</v>
       </c>
       <c r="L118">
-        <v>164.3390197753906</v>
+        <v>141.0891418457031</v>
       </c>
       <c r="M118">
-        <v>169.18647766113281</v>
+        <v>161.39595031738281</v>
       </c>
       <c r="N118">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="O118">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P118">
-        <v>2.5420157909393311</v>
+        <v>1.913353323936462</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.3">
@@ -6785,49 +6989,49 @@
         <v>133</v>
       </c>
       <c r="B119">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C119">
-        <v>0.35363790392875671</v>
+        <v>0.37599998712539667</v>
       </c>
       <c r="D119">
-        <v>14.887014389038089</v>
+        <v>22.870296478271481</v>
       </c>
       <c r="E119">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="F119">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="G119">
-        <v>1.1774724471428419</v>
+        <v>1.3683395121438511</v>
       </c>
       <c r="H119">
-        <v>0.16078431904315951</v>
+        <v>0.28235295414924622</v>
       </c>
       <c r="I119">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="J119">
-        <v>1.9450159072875981</v>
+        <v>2.2220110893249512</v>
       </c>
       <c r="K119">
-        <v>32.985065460205078</v>
+        <v>43.128086090087891</v>
       </c>
       <c r="L119">
-        <v>174.0622253417969</v>
+        <v>136.2134704589844</v>
       </c>
       <c r="M119">
-        <v>184.30607604980469</v>
+        <v>150.9937744140625</v>
       </c>
       <c r="N119">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="O119">
-        <v>222</v>
+        <v>186</v>
       </c>
       <c r="P119">
-        <v>1.9291757345199581</v>
+        <v>2.202363014221191</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.3">
@@ -6835,49 +7039,49 @@
         <v>134</v>
       </c>
       <c r="B120">
-        <v>15.3</v>
+        <v>10.9</v>
       </c>
       <c r="C120">
-        <v>0.40317460894584661</v>
+        <v>0.36923077702522278</v>
       </c>
       <c r="D120">
-        <v>27.872356414794918</v>
+        <v>21.019845962524411</v>
       </c>
       <c r="E120">
+        <v>187</v>
+      </c>
+      <c r="F120">
+        <v>146</v>
+      </c>
+      <c r="G120">
+        <v>1.30712381651375</v>
+      </c>
+      <c r="H120">
+        <v>0.23137255012989039</v>
+      </c>
+      <c r="I120">
         <v>199</v>
       </c>
-      <c r="F120">
-        <v>176</v>
-      </c>
-      <c r="G120">
-        <v>1.485931449716021</v>
-      </c>
-      <c r="H120">
-        <v>0.31764706969261169</v>
-      </c>
-      <c r="I120">
-        <v>211</v>
-      </c>
       <c r="J120">
-        <v>1.557840943336487</v>
+        <v>2.7219500541687012</v>
       </c>
       <c r="K120">
-        <v>43.782722473144531</v>
+        <v>34.080596923828118</v>
       </c>
       <c r="L120">
-        <v>154.1528015136719</v>
+        <v>154.58900451660159</v>
       </c>
       <c r="M120">
-        <v>149.82440185546881</v>
+        <v>166.68025207519531</v>
       </c>
       <c r="N120">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O120">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="P120">
-        <v>1.5225216150283809</v>
+        <v>2.196510791778564</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.3">
@@ -6888,46 +7092,46 @@
         <v>13.7</v>
       </c>
       <c r="C121">
-        <v>0.40816327929496771</v>
+        <v>0.38268157839775091</v>
       </c>
       <c r="D121">
-        <v>27.91140174865723</v>
+        <v>23.670562744140621</v>
       </c>
       <c r="E121">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="F121">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="G121">
-        <v>1.5217046809378829</v>
+        <v>1.417835958789702</v>
       </c>
       <c r="H121">
-        <v>0.33725491166114813</v>
+        <v>0.30980393290519709</v>
       </c>
       <c r="I121">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="J121">
-        <v>1.906749486923218</v>
+        <v>3.0619382858276372</v>
       </c>
       <c r="K121">
-        <v>41.570720672607422</v>
+        <v>35.911994934082031</v>
       </c>
       <c r="L121">
-        <v>144.271484375</v>
+        <v>126.3624954223633</v>
       </c>
       <c r="M121">
-        <v>140.3893737792969</v>
+        <v>142.02888488769531</v>
       </c>
       <c r="N121">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="O121">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="P121">
-        <v>1.8359746932983401</v>
+        <v>3.3251485824584961</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.3">
@@ -6935,49 +7139,49 @@
         <v>136</v>
       </c>
       <c r="B122">
-        <v>13.4</v>
+        <v>9.5</v>
       </c>
       <c r="C122">
-        <v>0.42231947183609009</v>
+        <v>0.36730360984802252</v>
       </c>
       <c r="D122">
-        <v>30.97480583190918</v>
+        <v>18.118867874145511</v>
       </c>
       <c r="E122">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="F122">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="G122">
-        <v>1.5848390981922691</v>
+        <v>1.269263900783413</v>
       </c>
       <c r="H122">
-        <v>0.37254902720451349</v>
+        <v>0.2431372553110123</v>
       </c>
       <c r="I122">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J122">
-        <v>2.1707956790924068</v>
+        <v>2.5245087146759029</v>
       </c>
       <c r="K122">
-        <v>32.185802459716797</v>
+        <v>36.4486083984375</v>
       </c>
       <c r="L122">
-        <v>148.41419982910159</v>
+        <v>137.85002136230469</v>
       </c>
       <c r="M122">
-        <v>142.70610046386719</v>
+        <v>152.06605529785159</v>
       </c>
       <c r="N122">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="O122">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P122">
-        <v>2.115007877349854</v>
+        <v>2.5477726459503169</v>
       </c>
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.3">
@@ -6985,49 +7189,49 @@
         <v>137</v>
       </c>
       <c r="B123">
-        <v>12.3</v>
+        <v>14.5</v>
       </c>
       <c r="C123">
-        <v>0.36741766333580023</v>
+        <v>0.41071429848670959</v>
       </c>
       <c r="D123">
-        <v>21.312627792358398</v>
+        <v>28.996530532836911</v>
       </c>
       <c r="E123">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="F123">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="G123">
-        <v>1.300896233601575</v>
+        <v>1.568913858687345</v>
       </c>
       <c r="H123">
-        <v>0.21960784494876859</v>
+        <v>0.37254902720451349</v>
       </c>
       <c r="I123">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="J123">
-        <v>1.8051682710647581</v>
+        <v>2.6367225646972661</v>
       </c>
       <c r="K123">
-        <v>36.747077941894531</v>
+        <v>37.533199310302727</v>
       </c>
       <c r="L123">
-        <v>167.5662841796875</v>
+        <v>132.1851501464844</v>
       </c>
       <c r="M123">
-        <v>172.96977233886719</v>
+        <v>138.40782165527341</v>
       </c>
       <c r="N123">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="O123">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="P123">
-        <v>1.861825108528137</v>
+        <v>2.6476984024047852</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.3">
@@ -7035,49 +7239,49 @@
         <v>138</v>
       </c>
       <c r="B124">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="C124">
-        <v>0.40062111616134638</v>
+        <v>0.36876356601715088</v>
       </c>
       <c r="D124">
-        <v>26.27456092834473</v>
+        <v>18.89896202087402</v>
       </c>
       <c r="E124">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="F124">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="G124">
-        <v>1.4818222360957229</v>
+        <v>1.287483841651186</v>
       </c>
       <c r="H124">
-        <v>0.30980393290519709</v>
+        <v>0.25490197539329529</v>
       </c>
       <c r="I124">
         <v>190</v>
       </c>
       <c r="J124">
-        <v>2.3216569423675542</v>
+        <v>2.4304051399230961</v>
       </c>
       <c r="K124">
-        <v>36.424285888671882</v>
+        <v>39.039325714111328</v>
       </c>
       <c r="L124">
-        <v>143.9951171875</v>
+        <v>133.473388671875</v>
       </c>
       <c r="M124">
-        <v>142.70887756347659</v>
+        <v>148.6822204589844</v>
       </c>
       <c r="N124">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O124">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="P124">
-        <v>1.9929960966110229</v>
+        <v>2.1974046230316162</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.3">
@@ -7085,49 +7289,49 @@
         <v>139</v>
       </c>
       <c r="B125">
-        <v>13.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="C125">
-        <v>0.36774194240570068</v>
+        <v>0.38679245114326483</v>
       </c>
       <c r="D125">
-        <v>18.80606651306152</v>
+        <v>21.161613464355469</v>
       </c>
       <c r="E125">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F125">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="G125">
-        <v>1.2668928050356361</v>
+        <v>1.3215298205311521</v>
       </c>
       <c r="H125">
-        <v>0.21568627655506131</v>
+        <v>0.27058824896812439</v>
       </c>
       <c r="I125">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J125">
-        <v>1.95127260684967</v>
+        <v>3.2145519256591801</v>
       </c>
       <c r="K125">
-        <v>44.045036315917969</v>
+        <v>39.887115478515618</v>
       </c>
       <c r="L125">
-        <v>157.42999267578119</v>
+        <v>155.17970275878909</v>
       </c>
       <c r="M125">
-        <v>164.9443664550781</v>
+        <v>162.68360900878909</v>
       </c>
       <c r="N125">
         <v>89</v>
       </c>
       <c r="O125">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="P125">
-        <v>1.8465176820755</v>
+        <v>2.5131568908691411</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.3">
@@ -7138,46 +7342,46 @@
         <v>13.7</v>
       </c>
       <c r="C126">
-        <v>0.38579654693603521</v>
+        <v>0.38218390941619867</v>
       </c>
       <c r="D126">
-        <v>24.631698608398441</v>
+        <v>24.563970565795898</v>
       </c>
       <c r="E126">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="F126">
-        <v>158</v>
+        <v>65</v>
       </c>
       <c r="G126">
-        <v>1.410862497335017</v>
+        <v>1.5167672913110939</v>
       </c>
       <c r="H126">
-        <v>0.27843138575553888</v>
+        <v>0.32941177487373352</v>
       </c>
       <c r="I126">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="J126">
-        <v>1.8869786262512209</v>
+        <v>2.3418736457824711</v>
       </c>
       <c r="K126">
-        <v>39.505348205566413</v>
+        <v>35.744338989257813</v>
       </c>
       <c r="L126">
-        <v>149.0213928222656</v>
+        <v>107.4327774047852</v>
       </c>
       <c r="M126">
-        <v>151.24632263183591</v>
+        <v>123.3224639892578</v>
       </c>
       <c r="N126">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="O126">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="P126">
-        <v>1.884158253669739</v>
+        <v>2.5404703617095952</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.3">
@@ -7185,49 +7389,49 @@
         <v>141</v>
       </c>
       <c r="B127">
-        <v>16.8</v>
+        <v>14.2</v>
       </c>
       <c r="C127">
-        <v>0.39300411939620972</v>
+        <v>0.3968254029750824</v>
       </c>
       <c r="D127">
-        <v>25.233028411865231</v>
+        <v>25.118356704711911</v>
       </c>
       <c r="E127">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="F127">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="G127">
-        <v>1.4218664886205981</v>
+        <v>1.4741267878682589</v>
       </c>
       <c r="H127">
-        <v>0.29019609093666082</v>
+        <v>0.36862745881080627</v>
       </c>
       <c r="I127">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="J127">
-        <v>2.8892335891723628</v>
+        <v>2.5601620674133301</v>
       </c>
       <c r="K127">
-        <v>39.625003814697273</v>
+        <v>41.261947631835938</v>
       </c>
       <c r="L127">
-        <v>153.9735107421875</v>
+        <v>119.348991394043</v>
       </c>
       <c r="M127">
-        <v>155.59468078613281</v>
+        <v>134.4701843261719</v>
       </c>
       <c r="N127">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="O127">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="P127">
-        <v>2.4494543075561519</v>
+        <v>2.557071208953857</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.3">
@@ -7235,49 +7439,49 @@
         <v>142</v>
       </c>
       <c r="B128">
-        <v>15.4</v>
+        <v>13.7</v>
       </c>
       <c r="C128">
-        <v>0.40782123804092407</v>
+        <v>0.37735849618911738</v>
       </c>
       <c r="D128">
-        <v>28.69630241394043</v>
+        <v>25.134853363037109</v>
       </c>
       <c r="E128">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="F128">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="G128">
-        <v>1.541052252431879</v>
+        <v>1.4299610793430939</v>
       </c>
       <c r="H128">
-        <v>0.35294118523597717</v>
+        <v>0.30980393290519709</v>
       </c>
       <c r="I128">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="J128">
-        <v>1.8947408199310301</v>
+        <v>1.967673063278198</v>
       </c>
       <c r="K128">
-        <v>43.745491027832031</v>
+        <v>41.521030426025391</v>
       </c>
       <c r="L128">
-        <v>138.96641540527341</v>
+        <v>128.5448913574219</v>
       </c>
       <c r="M128">
-        <v>141.23417663574219</v>
+        <v>147.0950622558594</v>
       </c>
       <c r="N128">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="O128">
         <v>190</v>
       </c>
       <c r="P128">
-        <v>1.867439746856689</v>
+        <v>1.9806144237518311</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.3">
@@ -7285,49 +7489,49 @@
         <v>143</v>
       </c>
       <c r="B129">
-        <v>14.7</v>
+        <v>11.9</v>
       </c>
       <c r="C129">
-        <v>0.37809917330741882</v>
+        <v>0.36418512463569641</v>
       </c>
       <c r="D129">
-        <v>22.855100631713871</v>
+        <v>20.67252349853516</v>
       </c>
       <c r="E129">
+        <v>160</v>
+      </c>
+      <c r="F129">
+        <v>99</v>
+      </c>
+      <c r="G129">
+        <v>1.334413901113553</v>
+      </c>
+      <c r="H129">
+        <v>0.27058824896812439</v>
+      </c>
+      <c r="I129">
         <v>190</v>
       </c>
-      <c r="F129">
-        <v>145</v>
-      </c>
-      <c r="G129">
-        <v>1.3466774566040061</v>
-      </c>
-      <c r="H129">
-        <v>0.26274511218070978</v>
-      </c>
-      <c r="I129">
-        <v>212</v>
-      </c>
       <c r="J129">
-        <v>2.116757869720459</v>
+        <v>2.0129325389862061</v>
       </c>
       <c r="K129">
-        <v>45.983524322509773</v>
+        <v>40.793598175048828</v>
       </c>
       <c r="L129">
-        <v>154.29936218261719</v>
+        <v>129.88792419433591</v>
       </c>
       <c r="M129">
-        <v>162.95140075683591</v>
+        <v>145.50030517578119</v>
       </c>
       <c r="N129">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="O129">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="P129">
-        <v>1.8628109693527219</v>
+        <v>1.8921282291412349</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.3">
@@ -7335,49 +7539,49 @@
         <v>144</v>
       </c>
       <c r="B130">
-        <v>14.3</v>
+        <v>13.4</v>
       </c>
       <c r="C130">
-        <v>0.40920096635818481</v>
+        <v>0.38347458839416498</v>
       </c>
       <c r="D130">
-        <v>25.63519287109375</v>
+        <v>25.792343139648441</v>
       </c>
       <c r="E130">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F130">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="G130">
-        <v>1.472243859890171</v>
+        <v>1.4591972498999799</v>
       </c>
       <c r="H130">
-        <v>0.3333333432674408</v>
+        <v>0.30588236451148992</v>
       </c>
       <c r="I130">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="J130">
-        <v>4.5170612335205078</v>
+        <v>2.3037161827087398</v>
       </c>
       <c r="K130">
-        <v>23.9613151550293</v>
+        <v>38.065650939941413</v>
       </c>
       <c r="L130">
-        <v>142.77952575683591</v>
+        <v>131.7486572265625</v>
       </c>
       <c r="M130">
-        <v>141.99479675292969</v>
+        <v>145.8208923339844</v>
       </c>
       <c r="N130">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="O130">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="P130">
-        <v>4.1668415069580078</v>
+        <v>2.3200531005859379</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.3">
@@ -7385,49 +7589,49 @@
         <v>145</v>
       </c>
       <c r="B131">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="C131">
-        <v>0.41780820488929749</v>
+        <v>0.37136465311050421</v>
       </c>
       <c r="D131">
-        <v>26.978157043457031</v>
+        <v>22.23245811462402</v>
       </c>
       <c r="E131">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F131">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="G131">
-        <v>1.529703665773448</v>
+        <v>1.34373167211704</v>
       </c>
       <c r="H131">
-        <v>0.34509804844856262</v>
+        <v>0.27450981736183172</v>
       </c>
       <c r="I131">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="J131">
-        <v>2.384699821472168</v>
+        <v>2.525464773178101</v>
       </c>
       <c r="K131">
-        <v>31.374626159667969</v>
+        <v>38.221080780029297</v>
       </c>
       <c r="L131">
-        <v>138.67567443847659</v>
+        <v>143.93247985839841</v>
       </c>
       <c r="M131">
-        <v>132.94325256347659</v>
+        <v>157.74974060058591</v>
       </c>
       <c r="N131">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="O131">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="P131">
-        <v>2.3245422840118408</v>
+        <v>2.146725177764893</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.3">
@@ -7435,49 +7639,49 @@
         <v>146</v>
       </c>
       <c r="B132">
-        <v>15.6</v>
+        <v>12.7</v>
       </c>
       <c r="C132">
-        <v>0.41164657473564148</v>
+        <v>0.36614173650741583</v>
       </c>
       <c r="D132">
-        <v>29.464740753173832</v>
+        <v>16.532464981079102</v>
       </c>
       <c r="E132">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="F132">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="G132">
-        <v>1.5646215765952629</v>
+        <v>1.249564444630622</v>
       </c>
       <c r="H132">
-        <v>0.35294118523597717</v>
+        <v>0.26666668057441711</v>
       </c>
       <c r="I132">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="J132">
-        <v>2.5675520896911621</v>
+        <v>1.953289151191711</v>
       </c>
       <c r="K132">
-        <v>27.36948394775391</v>
+        <v>51.355545043945313</v>
       </c>
       <c r="L132">
-        <v>141.20660400390619</v>
+        <v>127.5518112182617</v>
       </c>
       <c r="M132">
-        <v>140.56010437011719</v>
+        <v>141.41413879394531</v>
       </c>
       <c r="N132">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="O132">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="P132">
-        <v>2.581853866577148</v>
+        <v>1.793441534042358</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.3">
@@ -7485,49 +7689,49 @@
         <v>147</v>
       </c>
       <c r="B133">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="C133">
-        <v>0.37309643626213068</v>
+        <v>0.35447761416435242</v>
       </c>
       <c r="D133">
-        <v>22.42131233215332</v>
+        <v>15.68222808837891</v>
       </c>
       <c r="E133">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F133">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G133">
-        <v>1.362304242931716</v>
+        <v>1.2211610322990289</v>
       </c>
       <c r="H133">
-        <v>0.25490197539329529</v>
+        <v>0.24705882370471949</v>
       </c>
       <c r="I133">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="J133">
-        <v>1.793432831764221</v>
+        <v>2.0717356204986568</v>
       </c>
       <c r="K133">
-        <v>48.915924072265618</v>
+        <v>52.902389526367188</v>
       </c>
       <c r="L133">
-        <v>144.84535217285159</v>
+        <v>134.70817565917969</v>
       </c>
       <c r="M133">
-        <v>151.81996154785159</v>
+        <v>150.17921447753909</v>
       </c>
       <c r="N133">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="O133">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="P133">
-        <v>1.6993821859359739</v>
+        <v>1.904472827911377</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.3">
@@ -7535,49 +7739,49 @@
         <v>148</v>
       </c>
       <c r="B134">
-        <v>14.8</v>
+        <v>12.4</v>
       </c>
       <c r="C134">
-        <v>0.40211638808250427</v>
+        <v>0.40670859813690191</v>
       </c>
       <c r="D134">
-        <v>26.86655235290527</v>
+        <v>27.728826522827148</v>
       </c>
       <c r="E134">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="F134">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="G134">
-        <v>1.489930621933494</v>
+        <v>1.5673901726146919</v>
       </c>
       <c r="H134">
-        <v>0.32941177487373352</v>
+        <v>0.36078432202339172</v>
       </c>
       <c r="I134">
-        <v>194</v>
+        <v>162</v>
       </c>
       <c r="J134">
-        <v>2.104164838790894</v>
+        <v>3.27466869354248</v>
       </c>
       <c r="K134">
-        <v>36.294403076171882</v>
+        <v>33.899509429931641</v>
       </c>
       <c r="L134">
-        <v>139.62748718261719</v>
+        <v>122.8023376464844</v>
       </c>
       <c r="M134">
-        <v>143.78228759765619</v>
+        <v>132.3297424316406</v>
       </c>
       <c r="N134">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O134">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="P134">
-        <v>1.976390480995178</v>
+        <v>3.730744361877441</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.3">
@@ -7585,49 +7789,49 @@
         <v>149</v>
       </c>
       <c r="B135">
-        <v>14.9</v>
+        <v>12.6</v>
       </c>
       <c r="C135">
-        <v>0.38086304068565369</v>
+        <v>0.39056605100631708</v>
       </c>
       <c r="D135">
-        <v>24.679855346679691</v>
+        <v>24.4166259765625</v>
       </c>
       <c r="E135">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F135">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="G135">
-        <v>1.3709220263037949</v>
+        <v>1.386543748364379</v>
       </c>
       <c r="H135">
-        <v>0.27843138575553888</v>
+        <v>0.28235295414924622</v>
       </c>
       <c r="I135">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="J135">
-        <v>2.4446206092834468</v>
+        <v>4.0210552215576172</v>
       </c>
       <c r="K135">
-        <v>36.861377716064453</v>
+        <v>28.030525207519531</v>
       </c>
       <c r="L135">
-        <v>157.61846923828119</v>
+        <v>160.51799011230469</v>
       </c>
       <c r="M135">
-        <v>168.70758056640619</v>
+        <v>164.1476135253906</v>
       </c>
       <c r="N135">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="O135">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="P135">
-        <v>2.2684686183929439</v>
+        <v>3.0694296360015869</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.3">
@@ -7635,49 +7839,49 @@
         <v>150</v>
       </c>
       <c r="B136">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="C136">
-        <v>0.38065844774246221</v>
+        <v>0.37234041094779968</v>
       </c>
       <c r="D136">
-        <v>22.3840217590332</v>
+        <v>20.99424934387207</v>
       </c>
       <c r="E136">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="F136">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="G136">
-        <v>1.352740320860959</v>
+        <v>1.323239914226507</v>
       </c>
       <c r="H136">
-        <v>0.27450981736183172</v>
+        <v>0.27058824896812439</v>
       </c>
       <c r="I136">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J136">
-        <v>2.9507133960723881</v>
+        <v>2.3628542423248291</v>
       </c>
       <c r="K136">
-        <v>37.9407958984375</v>
+        <v>42.522579193115227</v>
       </c>
       <c r="L136">
-        <v>149.68739318847659</v>
+        <v>143.60475158691409</v>
       </c>
       <c r="M136">
-        <v>158.43263244628909</v>
+        <v>155.12562561035159</v>
       </c>
       <c r="N136">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O136">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="P136">
-        <v>2.3966012001037602</v>
+        <v>2.0149791240692139</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.3">
@@ -7685,49 +7889,49 @@
         <v>151</v>
       </c>
       <c r="B137">
-        <v>16.899999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="C137">
-        <v>0.40530303120613098</v>
+        <v>0.37330755591392523</v>
       </c>
       <c r="D137">
-        <v>27.243740081787109</v>
+        <v>22.324651718139648</v>
       </c>
       <c r="E137">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F137">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="G137">
-        <v>1.4954745013963631</v>
+        <v>1.328698859560999</v>
       </c>
       <c r="H137">
-        <v>0.32549020648002619</v>
+        <v>0.23921568691730499</v>
       </c>
       <c r="I137">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J137">
-        <v>2.7869381904602051</v>
+        <v>3.1383018493652339</v>
       </c>
       <c r="K137">
-        <v>29.577409744262699</v>
+        <v>23.788957595825199</v>
       </c>
       <c r="L137">
-        <v>146.67878723144531</v>
+        <v>156.7457275390625</v>
       </c>
       <c r="M137">
-        <v>146.05998229980469</v>
+        <v>168.5501708984375</v>
       </c>
       <c r="N137">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="O137">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="P137">
-        <v>2.522422075271606</v>
+        <v>2.5668244361877441</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
@@ -7735,49 +7939,49 @@
         <v>152</v>
       </c>
       <c r="B138">
-        <v>15.6</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="C138">
-        <v>0.45386534929275513</v>
+        <v>0.34565618634223938</v>
       </c>
       <c r="D138">
-        <v>32.4239501953125</v>
+        <v>14.27551364898682</v>
       </c>
       <c r="E138">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="F138">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G138">
-        <v>1.70720619025664</v>
+        <v>1.167221924727379</v>
       </c>
       <c r="H138">
-        <v>0.42352941632270807</v>
+        <v>0.18823529779911041</v>
       </c>
       <c r="I138">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="J138">
-        <v>3.496296882629395</v>
+        <v>2.3267571926116939</v>
       </c>
       <c r="K138">
-        <v>28.230531692504879</v>
+        <v>34.443943023681641</v>
       </c>
       <c r="L138">
-        <v>138.30134582519531</v>
+        <v>160.14442443847659</v>
       </c>
       <c r="M138">
-        <v>117.23597717285161</v>
+        <v>173.73362731933591</v>
       </c>
       <c r="N138">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="O138">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="P138">
-        <v>3.3484797477722168</v>
+        <v>1.891933917999268</v>
       </c>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
@@ -7785,49 +7989,49 @@
         <v>153</v>
       </c>
       <c r="B139">
-        <v>13.7</v>
+        <v>8.6</v>
       </c>
       <c r="C139">
-        <v>0.3617977499961853</v>
+        <v>0.34963768720626831</v>
       </c>
       <c r="D139">
-        <v>19.489559173583981</v>
+        <v>15.769749641418461</v>
       </c>
       <c r="E139">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F139">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G139">
-        <v>1.270724511370712</v>
+        <v>1.1833553271749839</v>
       </c>
       <c r="H139">
-        <v>0.21568627655506131</v>
+        <v>0.18431372940540311</v>
       </c>
       <c r="I139">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J139">
-        <v>1.9822483062744141</v>
+        <v>2.8535563945770259</v>
       </c>
       <c r="K139">
-        <v>44.140106201171882</v>
+        <v>38.438037872314453</v>
       </c>
       <c r="L139">
-        <v>155.7114562988281</v>
+        <v>167.5732727050781</v>
       </c>
       <c r="M139">
-        <v>166.73313903808591</v>
+        <v>182.7944030761719</v>
       </c>
       <c r="N139">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="O139">
         <v>221</v>
       </c>
       <c r="P139">
-        <v>1.799760580062866</v>
+        <v>2.2124092578887939</v>
       </c>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.3">
@@ -7835,49 +8039,49 @@
         <v>154</v>
       </c>
       <c r="B140">
-        <v>15.4</v>
+        <v>9.4</v>
       </c>
       <c r="C140">
-        <v>0.36475411057472229</v>
+        <v>0.37581700086593628</v>
       </c>
       <c r="D140">
-        <v>20.715530395507809</v>
+        <v>24.49101448059082</v>
       </c>
       <c r="E140">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F140">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="G140">
-        <v>1.2826160684638801</v>
+        <v>1.3977199622229171</v>
       </c>
       <c r="H140">
-        <v>0.20784313976764679</v>
+        <v>0.26666668057441711</v>
       </c>
       <c r="I140">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="J140">
-        <v>2.5035924911499019</v>
+        <v>2.2189610004425049</v>
       </c>
       <c r="K140">
-        <v>35.600521087646477</v>
+        <v>32.639450073242188</v>
       </c>
       <c r="L140">
-        <v>165.28089904785159</v>
+        <v>147.292724609375</v>
       </c>
       <c r="M140">
-        <v>175.3785705566406</v>
+        <v>156.4488830566406</v>
       </c>
       <c r="N140">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="O140">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="P140">
-        <v>2.3604907989501949</v>
+        <v>2.1850626468658452</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
@@ -7885,49 +8089,49 @@
         <v>155</v>
       </c>
       <c r="B141">
-        <v>9.8000000000000007</v>
+        <v>15.5</v>
       </c>
       <c r="C141">
-        <v>0.36654135584831238</v>
+        <v>0.39426523447036738</v>
       </c>
       <c r="D141">
-        <v>13.70323276519775</v>
+        <v>23.908050537109379</v>
       </c>
       <c r="E141">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F141">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="G141">
-        <v>1.1912468884299141</v>
+        <v>1.3964074946466589</v>
       </c>
       <c r="H141">
-        <v>0.20392157137393949</v>
+        <v>0.31372550129890442</v>
       </c>
       <c r="I141">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J141">
-        <v>2.2312970161437988</v>
+        <v>1.7796592712402339</v>
       </c>
       <c r="K141">
-        <v>39.159210205078118</v>
+        <v>47.499233245849609</v>
       </c>
       <c r="L141">
-        <v>155.7696838378906</v>
+        <v>148.44252014160159</v>
       </c>
       <c r="M141">
-        <v>160.8351135253906</v>
+        <v>152.2867736816406</v>
       </c>
       <c r="N141">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="O141">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="P141">
-        <v>1.942379236221313</v>
+        <v>1.6866122484207151</v>
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.3">
@@ -7935,49 +8139,49 @@
         <v>156</v>
       </c>
       <c r="B142">
-        <v>13</v>
+        <v>10.9</v>
       </c>
       <c r="C142">
-        <v>0.39344263076782232</v>
+        <v>0.3684210479259491</v>
       </c>
       <c r="D142">
-        <v>23.10604286193848</v>
+        <v>21.066268920898441</v>
       </c>
       <c r="E142">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F142">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="G142">
-        <v>1.360970582262067</v>
+        <v>1.287546069254482</v>
       </c>
       <c r="H142">
-        <v>0.29803922772407532</v>
+        <v>0.22745098173618319</v>
       </c>
       <c r="I142">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J142">
-        <v>2.2219669818878169</v>
+        <v>2.763277530670166</v>
       </c>
       <c r="K142">
-        <v>41.556964874267578</v>
+        <v>31.858089447021481</v>
       </c>
       <c r="L142">
-        <v>153.54609680175781</v>
+        <v>164.2817687988281</v>
       </c>
       <c r="M142">
-        <v>159.52217102050781</v>
+        <v>176.49797058105469</v>
       </c>
       <c r="N142">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="O142">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P142">
-        <v>1.997974634170532</v>
+        <v>2.446611642837524</v>
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
@@ -7985,49 +8189,49 @@
         <v>157</v>
       </c>
       <c r="B143">
-        <v>15.4</v>
+        <v>10.7</v>
       </c>
       <c r="C143">
-        <v>0.38841202855110168</v>
+        <v>0.36293435096740723</v>
       </c>
       <c r="D143">
-        <v>25.652240753173832</v>
+        <v>18.719144821166989</v>
       </c>
       <c r="E143">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F143">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G143">
-        <v>1.428014829928332</v>
+        <v>1.257477793388714</v>
       </c>
       <c r="H143">
-        <v>0.29019609093666082</v>
+        <v>0.20000000298023221</v>
       </c>
       <c r="I143">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J143">
-        <v>2.261658668518066</v>
+        <v>2.7884328365325932</v>
       </c>
       <c r="K143">
-        <v>32.64056396484375</v>
+        <v>28.98776817321777</v>
       </c>
       <c r="L143">
-        <v>148.92707824707031</v>
+        <v>162.92198181152341</v>
       </c>
       <c r="M143">
-        <v>155.57560729980469</v>
+        <v>172.64253234863281</v>
       </c>
       <c r="N143">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="O143">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="P143">
-        <v>2.2339892387390141</v>
+        <v>2.6085000038146968</v>
       </c>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
@@ -8035,49 +8239,49 @@
         <v>158</v>
       </c>
       <c r="B144">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="C144">
-        <v>0.38579654693603521</v>
+        <v>0.39842209219932562</v>
       </c>
       <c r="D144">
-        <v>24.725400924682621</v>
+        <v>22.51210784912109</v>
       </c>
       <c r="E144">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F144">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G144">
-        <v>1.3884802741868449</v>
+        <v>1.324099004800513</v>
       </c>
       <c r="H144">
-        <v>0.27450981736183172</v>
+        <v>0.30196079611778259</v>
       </c>
       <c r="I144">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="J144">
-        <v>2.803366899490356</v>
+        <v>2.149960994720459</v>
       </c>
       <c r="K144">
-        <v>31.258518218994141</v>
+        <v>31.642568588256839</v>
       </c>
       <c r="L144">
-        <v>155.9021301269531</v>
+        <v>162.47163391113281</v>
       </c>
       <c r="M144">
-        <v>163.1720275878906</v>
+        <v>171.57289123535159</v>
       </c>
       <c r="N144">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="O144">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="P144">
-        <v>2.6202692985534668</v>
+        <v>2.0069327354431148</v>
       </c>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.3">
@@ -8085,49 +8289,49 @@
         <v>159</v>
       </c>
       <c r="B145">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="C145">
-        <v>0.386892169713974</v>
+        <v>0.38576778769493097</v>
       </c>
       <c r="D145">
-        <v>23.010623931884769</v>
+        <v>25.596847534179691</v>
       </c>
       <c r="E145">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="F145">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="G145">
-        <v>1.3781123729554889</v>
+        <v>1.3996312464720591</v>
       </c>
       <c r="H145">
         <v>0.27450981736183172</v>
       </c>
       <c r="I145">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="J145">
-        <v>2.0251719951629639</v>
+        <v>2.0422277450561519</v>
       </c>
       <c r="K145">
-        <v>33.923904418945313</v>
+        <v>40.588550567626953</v>
       </c>
       <c r="L145">
-        <v>148.48077392578119</v>
+        <v>162.68666076660159</v>
       </c>
       <c r="M145">
-        <v>153.47715759277341</v>
+        <v>165.9930114746094</v>
       </c>
       <c r="N145">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="O145">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="P145">
-        <v>2.0194847583770752</v>
+        <v>1.9310842752456669</v>
       </c>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.3">
@@ -8135,49 +8339,49 @@
         <v>160</v>
       </c>
       <c r="B146">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="C146">
-        <v>0.39557740092277532</v>
+        <v>0.40000000596046448</v>
       </c>
       <c r="D146">
-        <v>25.786928176879879</v>
+        <v>27.58709716796875</v>
       </c>
       <c r="E146">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F146">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="G146">
-        <v>1.4285557752546429</v>
+        <v>1.4850146948342</v>
       </c>
       <c r="H146">
-        <v>0.30588236451148992</v>
+        <v>0.34509804844856262</v>
       </c>
       <c r="I146">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="J146">
-        <v>2.4989795684814449</v>
+        <v>1.9744527339935301</v>
       </c>
       <c r="K146">
-        <v>32.433280944824219</v>
+        <v>40.606281280517578</v>
       </c>
       <c r="L146">
-        <v>153.62542724609381</v>
+        <v>143.5341796875</v>
       </c>
       <c r="M146">
-        <v>157.45733642578119</v>
+        <v>149.8087463378906</v>
       </c>
       <c r="N146">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="O146">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P146">
-        <v>2.445165634155273</v>
+        <v>1.930024147033691</v>
       </c>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.3">
@@ -8185,49 +8389,49 @@
         <v>161</v>
       </c>
       <c r="B147">
-        <v>14.7</v>
+        <v>13.9</v>
       </c>
       <c r="C147">
-        <v>0.42888888716697687</v>
+        <v>0.38216561079025269</v>
       </c>
       <c r="D147">
-        <v>31.752092361450199</v>
+        <v>23.495622634887699</v>
       </c>
       <c r="E147">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F147">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="G147">
-        <v>1.630406886439639</v>
+        <v>1.372417098501225</v>
       </c>
       <c r="H147">
-        <v>0.38431373238563538</v>
+        <v>0.29803922772407532</v>
       </c>
       <c r="I147">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="J147">
-        <v>2.6412391662597661</v>
+        <v>2.2140343189239502</v>
       </c>
       <c r="K147">
-        <v>29.1689338684082</v>
+        <v>43.848976135253913</v>
       </c>
       <c r="L147">
-        <v>142.8977355957031</v>
+        <v>149.9082336425781</v>
       </c>
       <c r="M147">
-        <v>136.53092956542969</v>
+        <v>157.86280822753909</v>
       </c>
       <c r="N147">
         <v>86</v>
       </c>
       <c r="O147">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="P147">
-        <v>2.499730110168457</v>
+        <v>1.9753273725509639</v>
       </c>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.3">
@@ -8235,49 +8439,49 @@
         <v>162</v>
       </c>
       <c r="B148">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
       <c r="C148">
-        <v>0.37572255730628967</v>
+        <v>0.39720559120178223</v>
       </c>
       <c r="D148">
-        <v>21.24176025390625</v>
+        <v>28.31387901306152</v>
       </c>
       <c r="E148">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F148">
         <v>150</v>
       </c>
       <c r="G148">
-        <v>1.30457768074617</v>
+        <v>1.5203498336598571</v>
       </c>
       <c r="H148">
-        <v>0.25490197539329529</v>
+        <v>0.32156863808631903</v>
       </c>
       <c r="I148">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="J148">
-        <v>2.3152287006378169</v>
+        <v>2.2339644432067871</v>
       </c>
       <c r="K148">
-        <v>36.207836151123047</v>
+        <v>36.657508850097663</v>
       </c>
       <c r="L148">
-        <v>158.5896911621094</v>
+        <v>141.99591064453119</v>
       </c>
       <c r="M148">
-        <v>168.76707458496091</v>
+        <v>145.260009765625</v>
       </c>
       <c r="N148">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="O148">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="P148">
-        <v>2.0614430904388432</v>
+        <v>2.1603293418884282</v>
       </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.3">
@@ -8285,49 +8489,49 @@
         <v>163</v>
       </c>
       <c r="B149">
-        <v>15.2</v>
+        <v>15.7</v>
       </c>
       <c r="C149">
-        <v>0.39747634530067438</v>
+        <v>0.40372669696807861</v>
       </c>
       <c r="D149">
-        <v>28.7714958190918</v>
+        <v>25.960237503051761</v>
       </c>
       <c r="E149">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F149">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G149">
-        <v>1.507987622526157</v>
+        <v>1.458164351213175</v>
       </c>
       <c r="H149">
-        <v>0.32156863808631903</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="I149">
+        <v>201</v>
+      </c>
+      <c r="J149">
+        <v>1.866783499717712</v>
+      </c>
+      <c r="K149">
+        <v>39.183685302734382</v>
+      </c>
+      <c r="L149">
+        <v>146.57997131347659</v>
+      </c>
+      <c r="M149">
+        <v>146.33161926269531</v>
+      </c>
+      <c r="N149">
+        <v>81</v>
+      </c>
+      <c r="O149">
         <v>192</v>
       </c>
-      <c r="J149">
-        <v>2.7258157730102539</v>
-      </c>
-      <c r="K149">
-        <v>34.550453186035163</v>
-      </c>
-      <c r="L149">
-        <v>148.827880859375</v>
-      </c>
-      <c r="M149">
-        <v>151.88177490234381</v>
-      </c>
-      <c r="N149">
-        <v>91</v>
-      </c>
-      <c r="O149">
-        <v>184</v>
-      </c>
       <c r="P149">
-        <v>2.3145232200622559</v>
+        <v>1.7682920694351201</v>
       </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.3">
@@ -8335,48 +8539,3448 @@
         <v>164</v>
       </c>
       <c r="B150">
-        <v>15.5</v>
+        <v>13.9</v>
       </c>
       <c r="C150">
-        <v>0.37556561827659612</v>
+        <v>0.39832285046577448</v>
       </c>
       <c r="D150">
-        <v>20.871810913085941</v>
+        <v>24.08180046081543</v>
       </c>
       <c r="E150">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F150">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="G150">
-        <v>1.321825264096262</v>
+        <v>1.4125228870140529</v>
       </c>
       <c r="H150">
-        <v>0.23529411852359769</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="I150">
         <v>211</v>
       </c>
       <c r="J150">
+        <v>2.1067130565643311</v>
+      </c>
+      <c r="K150">
+        <v>44.787300109863281</v>
+      </c>
+      <c r="L150">
+        <v>139.5755615234375</v>
+      </c>
+      <c r="M150">
+        <v>146.28221130371091</v>
+      </c>
+      <c r="N150">
+        <v>73</v>
+      </c>
+      <c r="O150">
+        <v>191</v>
+      </c>
+      <c r="P150">
+        <v>2.0649490356445308</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>165</v>
+      </c>
+      <c r="B151">
+        <v>13.6</v>
+      </c>
+      <c r="C151">
+        <v>0.4077448844909668</v>
+      </c>
+      <c r="D151">
+        <v>27.309881210327148</v>
+      </c>
+      <c r="E151">
+        <v>186</v>
+      </c>
+      <c r="F151">
+        <v>158</v>
+      </c>
+      <c r="G151">
+        <v>1.4684998160165641</v>
+      </c>
+      <c r="H151">
+        <v>0.35686275362968439</v>
+      </c>
+      <c r="I151">
+        <v>203</v>
+      </c>
+      <c r="J151">
+        <v>2.3577249050140381</v>
+      </c>
+      <c r="K151">
+        <v>38.945327758789063</v>
+      </c>
+      <c r="L151">
+        <v>146.65687561035159</v>
+      </c>
+      <c r="M151">
+        <v>152.46490478515619</v>
+      </c>
+      <c r="N151">
+        <v>91</v>
+      </c>
+      <c r="O151">
+        <v>194</v>
+      </c>
+      <c r="P151">
+        <v>2.1593103408813481</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>166</v>
+      </c>
+      <c r="B152">
+        <v>15.4</v>
+      </c>
+      <c r="C152">
+        <v>0.4309927225112915</v>
+      </c>
+      <c r="D152">
+        <v>30.629327774047852</v>
+      </c>
+      <c r="E152">
+        <v>189</v>
+      </c>
+      <c r="F152">
+        <v>159</v>
+      </c>
+      <c r="G152">
+        <v>1.613227238970306</v>
+      </c>
+      <c r="H152">
+        <v>0.40392157435417181</v>
+      </c>
+      <c r="I152">
+        <v>187</v>
+      </c>
+      <c r="J152">
+        <v>2.2642586231231689</v>
+      </c>
+      <c r="K152">
+        <v>35.053558349609382</v>
+      </c>
+      <c r="L152">
+        <v>139.2833557128906</v>
+      </c>
+      <c r="M152">
+        <v>133.69749450683591</v>
+      </c>
+      <c r="N152">
+        <v>73</v>
+      </c>
+      <c r="O152">
+        <v>171</v>
+      </c>
+      <c r="P152">
+        <v>2.1944301128387451</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>167</v>
+      </c>
+      <c r="B153">
+        <v>13.7</v>
+      </c>
+      <c r="C153">
+        <v>0.40217390656471252</v>
+      </c>
+      <c r="D153">
+        <v>27.657648086547852</v>
+      </c>
+      <c r="E153">
+        <v>190</v>
+      </c>
+      <c r="F153">
+        <v>152</v>
+      </c>
+      <c r="G153">
+        <v>1.501837667485576</v>
+      </c>
+      <c r="H153">
+        <v>0.32156863808631903</v>
+      </c>
+      <c r="I153">
+        <v>197</v>
+      </c>
+      <c r="J153">
+        <v>2.0546867847442631</v>
+      </c>
+      <c r="K153">
+        <v>36.779342651367188</v>
+      </c>
+      <c r="L153">
+        <v>145.32814025878909</v>
+      </c>
+      <c r="M153">
+        <v>144.77545166015619</v>
+      </c>
+      <c r="N153">
+        <v>78</v>
+      </c>
+      <c r="O153">
+        <v>184</v>
+      </c>
+      <c r="P153">
+        <v>2.06242847442627</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>168</v>
+      </c>
+      <c r="B154">
+        <v>11.7</v>
+      </c>
+      <c r="C154">
+        <v>0.37119674682617188</v>
+      </c>
+      <c r="D154">
+        <v>18.269975662231449</v>
+      </c>
+      <c r="E154">
+        <v>184</v>
+      </c>
+      <c r="F154">
+        <v>129</v>
+      </c>
+      <c r="G154">
+        <v>1.2723077201798501</v>
+      </c>
+      <c r="H154">
+        <v>0.23529411852359769</v>
+      </c>
+      <c r="I154">
+        <v>192</v>
+      </c>
+      <c r="J154">
+        <v>2.2893285751342769</v>
+      </c>
+      <c r="K154">
+        <v>31.927253723144531</v>
+      </c>
+      <c r="L154">
+        <v>150.75238037109381</v>
+      </c>
+      <c r="M154">
+        <v>158.65904235839841</v>
+      </c>
+      <c r="N154">
+        <v>108</v>
+      </c>
+      <c r="O154">
+        <v>189</v>
+      </c>
+      <c r="P154">
+        <v>2.0367121696472168</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>169</v>
+      </c>
+      <c r="B155">
+        <v>13.3</v>
+      </c>
+      <c r="C155">
+        <v>0.4004376232624054</v>
+      </c>
+      <c r="D155">
+        <v>23.049478530883789</v>
+      </c>
+      <c r="E155">
+        <v>198</v>
+      </c>
+      <c r="F155">
+        <v>156</v>
+      </c>
+      <c r="G155">
+        <v>1.3843463825330391</v>
+      </c>
+      <c r="H155">
+        <v>0.30196079611778259</v>
+      </c>
+      <c r="I155">
+        <v>204</v>
+      </c>
+      <c r="J155">
+        <v>2.115591287612915</v>
+      </c>
+      <c r="K155">
+        <v>38.629871368408203</v>
+      </c>
+      <c r="L155">
+        <v>155.578125</v>
+      </c>
+      <c r="M155">
+        <v>152.97264099121091</v>
+      </c>
+      <c r="N155">
+        <v>85</v>
+      </c>
+      <c r="O155">
+        <v>198</v>
+      </c>
+      <c r="P155">
+        <v>1.907040119171143</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>170</v>
+      </c>
+      <c r="B156">
+        <v>13.9</v>
+      </c>
+      <c r="C156">
+        <v>0.41067284345626831</v>
+      </c>
+      <c r="D156">
+        <v>26.12821197509766</v>
+      </c>
+      <c r="E156">
+        <v>184</v>
+      </c>
+      <c r="F156">
+        <v>152</v>
+      </c>
+      <c r="G156">
+        <v>1.4704355598155709</v>
+      </c>
+      <c r="H156">
+        <v>0.34117648005485529</v>
+      </c>
+      <c r="I156">
+        <v>187</v>
+      </c>
+      <c r="J156">
+        <v>3.0173766613006592</v>
+      </c>
+      <c r="K156">
+        <v>32.034500122070313</v>
+      </c>
+      <c r="L156">
+        <v>141.99156188964841</v>
+      </c>
+      <c r="M156">
+        <v>144.68293762207031</v>
+      </c>
+      <c r="N156">
+        <v>97</v>
+      </c>
+      <c r="O156">
+        <v>170</v>
+      </c>
+      <c r="P156">
+        <v>2.816193580627441</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>171</v>
+      </c>
+      <c r="B157">
+        <v>15</v>
+      </c>
+      <c r="C157">
+        <v>0.39045554399490362</v>
+      </c>
+      <c r="D157">
+        <v>24.332571029663089</v>
+      </c>
+      <c r="E157">
+        <v>193</v>
+      </c>
+      <c r="F157">
+        <v>157</v>
+      </c>
+      <c r="G157">
+        <v>1.3988519982415859</v>
+      </c>
+      <c r="H157">
+        <v>0.29019609093666082</v>
+      </c>
+      <c r="I157">
+        <v>213</v>
+      </c>
+      <c r="J157">
+        <v>2.0024344921112061</v>
+      </c>
+      <c r="K157">
+        <v>41.317085266113281</v>
+      </c>
+      <c r="L157">
+        <v>152.466796875</v>
+      </c>
+      <c r="M157">
+        <v>154.82867431640619</v>
+      </c>
+      <c r="N157">
+        <v>76</v>
+      </c>
+      <c r="O157">
+        <v>199</v>
+      </c>
+      <c r="P157">
+        <v>1.975751638412476</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>172</v>
+      </c>
+      <c r="B158">
+        <v>14.7</v>
+      </c>
+      <c r="C158">
+        <v>0.41689372062683111</v>
+      </c>
+      <c r="D158">
+        <v>31.705753326416019</v>
+      </c>
+      <c r="E158">
+        <v>192</v>
+      </c>
+      <c r="F158">
+        <v>153</v>
+      </c>
+      <c r="G158">
+        <v>1.650299166989438</v>
+      </c>
+      <c r="H158">
+        <v>0.37254902720451349</v>
+      </c>
+      <c r="I158">
+        <v>179</v>
+      </c>
+      <c r="J158">
+        <v>2.33311939239502</v>
+      </c>
+      <c r="K158">
+        <v>32.701877593994141</v>
+      </c>
+      <c r="L158">
+        <v>136.3662109375</v>
+      </c>
+      <c r="M158">
+        <v>134.03715515136719</v>
+      </c>
+      <c r="N158">
+        <v>69</v>
+      </c>
+      <c r="O158">
+        <v>165</v>
+      </c>
+      <c r="P158">
+        <v>2.2482049465179439</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>173</v>
+      </c>
+      <c r="B159">
+        <v>15.4</v>
+      </c>
+      <c r="C159">
+        <v>0.40446650981903082</v>
+      </c>
+      <c r="D159">
+        <v>28.469297409057621</v>
+      </c>
+      <c r="E159">
+        <v>185</v>
+      </c>
+      <c r="F159">
+        <v>119</v>
+      </c>
+      <c r="G159">
+        <v>1.568115973928732</v>
+      </c>
+      <c r="H159">
+        <v>0.3333333432674408</v>
+      </c>
+      <c r="I159">
+        <v>189</v>
+      </c>
+      <c r="J159">
+        <v>2.1085994243621831</v>
+      </c>
+      <c r="K159">
+        <v>40.986747741699219</v>
+      </c>
+      <c r="L159">
+        <v>134.51336669921881</v>
+      </c>
+      <c r="M159">
+        <v>132.7209167480469</v>
+      </c>
+      <c r="N159">
+        <v>68</v>
+      </c>
+      <c r="O159">
+        <v>175</v>
+      </c>
+      <c r="P159">
+        <v>2.0384092330932622</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>174</v>
+      </c>
+      <c r="B160">
+        <v>14.9</v>
+      </c>
+      <c r="C160">
+        <v>0.43023255467414862</v>
+      </c>
+      <c r="D160">
+        <v>29.062643051147461</v>
+      </c>
+      <c r="E160">
+        <v>194</v>
+      </c>
+      <c r="F160">
+        <v>143</v>
+      </c>
+      <c r="G160">
+        <v>1.600290464969607</v>
+      </c>
+      <c r="H160">
+        <v>0.37254902720451349</v>
+      </c>
+      <c r="I160">
+        <v>175</v>
+      </c>
+      <c r="J160">
+        <v>2.359338760375977</v>
+      </c>
+      <c r="K160">
+        <v>28.5696907043457</v>
+      </c>
+      <c r="L160">
+        <v>138.5892639160156</v>
+      </c>
+      <c r="M160">
+        <v>127.7242050170898</v>
+      </c>
+      <c r="N160">
+        <v>81</v>
+      </c>
+      <c r="O160">
+        <v>156</v>
+      </c>
+      <c r="P160">
+        <v>2.1780951023101811</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>175</v>
+      </c>
+      <c r="B161">
+        <v>14.1</v>
+      </c>
+      <c r="C161">
+        <v>0.37179487943649292</v>
+      </c>
+      <c r="D161">
+        <v>18.428304672241211</v>
+      </c>
+      <c r="E161">
+        <v>193</v>
+      </c>
+      <c r="F161">
+        <v>117</v>
+      </c>
+      <c r="G161">
+        <v>1.262021813270181</v>
+      </c>
+      <c r="H161">
+        <v>0.24705882370471949</v>
+      </c>
+      <c r="I161">
+        <v>202</v>
+      </c>
+      <c r="J161">
+        <v>2.7597122192382808</v>
+      </c>
+      <c r="K161">
+        <v>35.961315155029297</v>
+      </c>
+      <c r="L161">
+        <v>155.97340393066409</v>
+      </c>
+      <c r="M161">
+        <v>165.37214660644531</v>
+      </c>
+      <c r="N161">
+        <v>109</v>
+      </c>
+      <c r="O161">
+        <v>195</v>
+      </c>
+      <c r="P161">
+        <v>2.4143316745758061</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>176</v>
+      </c>
+      <c r="B162">
+        <v>14.1</v>
+      </c>
+      <c r="C162">
+        <v>0.40900194644927979</v>
+      </c>
+      <c r="D162">
+        <v>29.26578330993652</v>
+      </c>
+      <c r="E162">
+        <v>209</v>
+      </c>
+      <c r="F162">
+        <v>189</v>
+      </c>
+      <c r="G162">
+        <v>1.5003082551171381</v>
+      </c>
+      <c r="H162">
+        <v>0.32549020648002619</v>
+      </c>
+      <c r="I162">
+        <v>204</v>
+      </c>
+      <c r="J162">
+        <v>2.2975947856903081</v>
+      </c>
+      <c r="K162">
+        <v>32.328346252441413</v>
+      </c>
+      <c r="L162">
+        <v>161.1357116699219</v>
+      </c>
+      <c r="M162">
+        <v>156.69476318359381</v>
+      </c>
+      <c r="N162">
+        <v>96</v>
+      </c>
+      <c r="O162">
+        <v>192</v>
+      </c>
+      <c r="P162">
+        <v>2.270307302474976</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>177</v>
+      </c>
+      <c r="B163">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C163">
+        <v>0.36363637447357178</v>
+      </c>
+      <c r="D163">
+        <v>21.4205436706543</v>
+      </c>
+      <c r="E163">
+        <v>193</v>
+      </c>
+      <c r="F163">
+        <v>163</v>
+      </c>
+      <c r="G163">
+        <v>1.2958273971516669</v>
+      </c>
+      <c r="H163">
+        <v>0.21960784494876859</v>
+      </c>
+      <c r="I163">
+        <v>215</v>
+      </c>
+      <c r="J163">
+        <v>2.1911964416503911</v>
+      </c>
+      <c r="K163">
+        <v>39.862201690673828</v>
+      </c>
+      <c r="L163">
+        <v>164.00315856933591</v>
+      </c>
+      <c r="M163">
+        <v>174.9908752441406</v>
+      </c>
+      <c r="N163">
+        <v>96</v>
+      </c>
+      <c r="O163">
+        <v>219</v>
+      </c>
+      <c r="P163">
+        <v>2.104111909866333</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>178</v>
+      </c>
+      <c r="B164">
+        <v>15.1</v>
+      </c>
+      <c r="C164">
+        <v>0.40122199058532709</v>
+      </c>
+      <c r="D164">
+        <v>23.419643402099609</v>
+      </c>
+      <c r="E164">
+        <v>193</v>
+      </c>
+      <c r="F164">
+        <v>151</v>
+      </c>
+      <c r="G164">
+        <v>1.3990718861779019</v>
+      </c>
+      <c r="H164">
+        <v>0.30588236451148992</v>
+      </c>
+      <c r="I164">
+        <v>207</v>
+      </c>
+      <c r="J164">
+        <v>2.4576847553253169</v>
+      </c>
+      <c r="K164">
+        <v>39.395484924316413</v>
+      </c>
+      <c r="L164">
+        <v>150.6950988769531</v>
+      </c>
+      <c r="M164">
+        <v>150.1626892089844</v>
+      </c>
+      <c r="N164">
+        <v>83</v>
+      </c>
+      <c r="O164">
+        <v>188</v>
+      </c>
+      <c r="P164">
+        <v>2.261107444763184</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>179</v>
+      </c>
+      <c r="B165">
+        <v>11.6</v>
+      </c>
+      <c r="C165">
+        <v>0.37109375</v>
+      </c>
+      <c r="D165">
+        <v>22.126142501831051</v>
+      </c>
+      <c r="E165">
+        <v>182</v>
+      </c>
+      <c r="F165">
+        <v>166</v>
+      </c>
+      <c r="G165">
+        <v>1.3226036386288</v>
+      </c>
+      <c r="H165">
+        <v>0.24705882370471949</v>
+      </c>
+      <c r="I165">
+        <v>183</v>
+      </c>
+      <c r="J165">
+        <v>3.8973085880279541</v>
+      </c>
+      <c r="K165">
+        <v>21.66053581237793</v>
+      </c>
+      <c r="L165">
+        <v>154.4453125</v>
+      </c>
+      <c r="M165">
+        <v>168.3892517089844</v>
+      </c>
+      <c r="N165">
+        <v>137</v>
+      </c>
+      <c r="O165">
+        <v>186</v>
+      </c>
+      <c r="P165">
+        <v>3.151129007339478</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>180</v>
+      </c>
+      <c r="B166">
+        <v>15.3</v>
+      </c>
+      <c r="C166">
+        <v>0.39851483702659612</v>
+      </c>
+      <c r="D166">
+        <v>22.846548080444339</v>
+      </c>
+      <c r="E166">
+        <v>195</v>
+      </c>
+      <c r="F166">
+        <v>126</v>
+      </c>
+      <c r="G166">
+        <v>1.389383545194862</v>
+      </c>
+      <c r="H166">
+        <v>0.31372550129890442</v>
+      </c>
+      <c r="I166">
+        <v>200</v>
+      </c>
+      <c r="J166">
+        <v>2.6938433647155762</v>
+      </c>
+      <c r="K166">
+        <v>42.098976135253913</v>
+      </c>
+      <c r="L166">
+        <v>147.86381530761719</v>
+      </c>
+      <c r="M166">
+        <v>149.15946960449219</v>
+      </c>
+      <c r="N166">
+        <v>75</v>
+      </c>
+      <c r="O166">
+        <v>187</v>
+      </c>
+      <c r="P166">
+        <v>2.1817536354064941</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>181</v>
+      </c>
+      <c r="B167">
+        <v>13.9</v>
+      </c>
+      <c r="C167">
+        <v>0.40286299586296082</v>
+      </c>
+      <c r="D167">
+        <v>28.446718215942379</v>
+      </c>
+      <c r="E167">
+        <v>196</v>
+      </c>
+      <c r="F167">
+        <v>164</v>
+      </c>
+      <c r="G167">
+        <v>1.5025420876922311</v>
+      </c>
+      <c r="H167">
+        <v>0.33725491166114813</v>
+      </c>
+      <c r="I167">
+        <v>207</v>
+      </c>
+      <c r="J167">
+        <v>2.163744211196899</v>
+      </c>
+      <c r="K167">
+        <v>37.857139587402337</v>
+      </c>
+      <c r="L167">
+        <v>149.86033630371091</v>
+      </c>
+      <c r="M167">
+        <v>150.47395324707031</v>
+      </c>
+      <c r="N167">
+        <v>84</v>
+      </c>
+      <c r="O167">
+        <v>187</v>
+      </c>
+      <c r="P167">
+        <v>2.0751328468322749</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>182</v>
+      </c>
+      <c r="B168">
+        <v>14.4</v>
+      </c>
+      <c r="C168">
+        <v>0.41299790143966669</v>
+      </c>
+      <c r="D168">
+        <v>28.098196029663089</v>
+      </c>
+      <c r="E168">
+        <v>200</v>
+      </c>
+      <c r="F168">
+        <v>164</v>
+      </c>
+      <c r="G168">
+        <v>1.501295801388431</v>
+      </c>
+      <c r="H168">
+        <v>0.3490196168422699</v>
+      </c>
+      <c r="I168">
+        <v>209</v>
+      </c>
+      <c r="J168">
+        <v>2.1504542827606201</v>
+      </c>
+      <c r="K168">
+        <v>37.744338989257813</v>
+      </c>
+      <c r="L168">
+        <v>151.2465515136719</v>
+      </c>
+      <c r="M168">
+        <v>148.4222106933594</v>
+      </c>
+      <c r="N168">
+        <v>89</v>
+      </c>
+      <c r="O168">
+        <v>187</v>
+      </c>
+      <c r="P168">
+        <v>2.070000171661377</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>183</v>
+      </c>
+      <c r="B169">
+        <v>15.1</v>
+      </c>
+      <c r="C169">
+        <v>0.40709811449050898</v>
+      </c>
+      <c r="D169">
+        <v>29.878969192504879</v>
+      </c>
+      <c r="E169">
+        <v>186</v>
+      </c>
+      <c r="F169">
+        <v>161</v>
+      </c>
+      <c r="G169">
+        <v>1.561008743712569</v>
+      </c>
+      <c r="H169">
+        <v>0.35294118523597717</v>
+      </c>
+      <c r="I169">
+        <v>176</v>
+      </c>
+      <c r="J169">
+        <v>3.1164038181304932</v>
+      </c>
+      <c r="K169">
+        <v>26.981931686401371</v>
+      </c>
+      <c r="L169">
+        <v>140.36683654785159</v>
+      </c>
+      <c r="M169">
+        <v>145.02928161621091</v>
+      </c>
+      <c r="N169">
+        <v>101</v>
+      </c>
+      <c r="O169">
+        <v>168</v>
+      </c>
+      <c r="P169">
+        <v>3.1335291862487789</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>184</v>
+      </c>
+      <c r="B170">
+        <v>15.3</v>
+      </c>
+      <c r="C170">
+        <v>0.39325842261314392</v>
+      </c>
+      <c r="D170">
+        <v>25.51174354553223</v>
+      </c>
+      <c r="E170">
+        <v>197</v>
+      </c>
+      <c r="F170">
+        <v>146</v>
+      </c>
+      <c r="G170">
+        <v>1.445151489156105</v>
+      </c>
+      <c r="H170">
+        <v>0.29411765933036799</v>
+      </c>
+      <c r="I170">
+        <v>210</v>
+      </c>
+      <c r="J170">
+        <v>1.986564040184021</v>
+      </c>
+      <c r="K170">
+        <v>42.914539337158203</v>
+      </c>
+      <c r="L170">
+        <v>150.8766784667969</v>
+      </c>
+      <c r="M170">
+        <v>147.53900146484381</v>
+      </c>
+      <c r="N170">
+        <v>72</v>
+      </c>
+      <c r="O170">
+        <v>194</v>
+      </c>
+      <c r="P170">
+        <v>1.8946355581283569</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>185</v>
+      </c>
+      <c r="B171">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="C171">
+        <v>0.38955822587013239</v>
+      </c>
+      <c r="D171">
+        <v>25.536233901977539</v>
+      </c>
+      <c r="E171">
+        <v>198</v>
+      </c>
+      <c r="F171">
+        <v>116</v>
+      </c>
+      <c r="G171">
+        <v>1.438157966543113</v>
+      </c>
+      <c r="H171">
+        <v>0.29019609093666082</v>
+      </c>
+      <c r="I171">
+        <v>198</v>
+      </c>
+      <c r="J171">
+        <v>2.5403785705566411</v>
+      </c>
+      <c r="K171">
+        <v>43.481307983398438</v>
+      </c>
+      <c r="L171">
+        <v>147.88011169433591</v>
+      </c>
+      <c r="M171">
+        <v>151.2971496582031</v>
+      </c>
+      <c r="N171">
+        <v>68</v>
+      </c>
+      <c r="O171">
+        <v>196</v>
+      </c>
+      <c r="P171">
+        <v>2.0240767002105708</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>186</v>
+      </c>
+      <c r="B172">
+        <v>13.2</v>
+      </c>
+      <c r="C172">
+        <v>0.3844660222530365</v>
+      </c>
+      <c r="D172">
+        <v>22.450162887573239</v>
+      </c>
+      <c r="E172">
+        <v>193</v>
+      </c>
+      <c r="F172">
+        <v>141</v>
+      </c>
+      <c r="G172">
+        <v>1.3594238878082241</v>
+      </c>
+      <c r="H172">
+        <v>0.26666668057441711</v>
+      </c>
+      <c r="I172">
+        <v>213</v>
+      </c>
+      <c r="J172">
+        <v>2.1066691875457759</v>
+      </c>
+      <c r="K172">
+        <v>40.623622894287109</v>
+      </c>
+      <c r="L172">
+        <v>155.24177551269531</v>
+      </c>
+      <c r="M172">
+        <v>157.7576599121094</v>
+      </c>
+      <c r="N172">
+        <v>93</v>
+      </c>
+      <c r="O172">
+        <v>195</v>
+      </c>
+      <c r="P172">
+        <v>2.0218064785003662</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>187</v>
+      </c>
+      <c r="B173">
+        <v>13.5</v>
+      </c>
+      <c r="C173">
+        <v>0.40408164262771612</v>
+      </c>
+      <c r="D173">
+        <v>24.64246940612793</v>
+      </c>
+      <c r="E173">
+        <v>201</v>
+      </c>
+      <c r="F173">
+        <v>178</v>
+      </c>
+      <c r="G173">
+        <v>1.408326288044482</v>
+      </c>
+      <c r="H173">
+        <v>0.30980393290519709</v>
+      </c>
+      <c r="I173">
+        <v>205</v>
+      </c>
+      <c r="J173">
+        <v>2.2150595188140869</v>
+      </c>
+      <c r="K173">
+        <v>33.741451263427727</v>
+      </c>
+      <c r="L173">
+        <v>159.2691955566406</v>
+      </c>
+      <c r="M173">
+        <v>155.98907470703119</v>
+      </c>
+      <c r="N173">
+        <v>96</v>
+      </c>
+      <c r="O173">
+        <v>195</v>
+      </c>
+      <c r="P173">
+        <v>2.072587251663208</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>188</v>
+      </c>
+      <c r="B174">
+        <v>15</v>
+      </c>
+      <c r="C174">
+        <v>0.41079813241958618</v>
+      </c>
+      <c r="D174">
+        <v>27.889167785644531</v>
+      </c>
+      <c r="E174">
+        <v>188</v>
+      </c>
+      <c r="F174">
+        <v>154</v>
+      </c>
+      <c r="G174">
+        <v>1.526324962768459</v>
+      </c>
+      <c r="H174">
+        <v>0.34117648005485529</v>
+      </c>
+      <c r="I174">
+        <v>201</v>
+      </c>
+      <c r="J174">
+        <v>2.0029277801513672</v>
+      </c>
+      <c r="K174">
+        <v>36.829135894775391</v>
+      </c>
+      <c r="L174">
+        <v>143.01554870605469</v>
+      </c>
+      <c r="M174">
+        <v>139.43443298339841</v>
+      </c>
+      <c r="N174">
+        <v>81</v>
+      </c>
+      <c r="O174">
+        <v>175</v>
+      </c>
+      <c r="P174">
+        <v>2.068879365921021</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>189</v>
+      </c>
+      <c r="B175">
+        <v>15.5</v>
+      </c>
+      <c r="C175">
+        <v>0.40890687704086298</v>
+      </c>
+      <c r="D175">
+        <v>27.528945922851559</v>
+      </c>
+      <c r="E175">
+        <v>188</v>
+      </c>
+      <c r="F175">
+        <v>163</v>
+      </c>
+      <c r="G175">
+        <v>1.4927820566063099</v>
+      </c>
+      <c r="H175">
+        <v>0.34117648005485529</v>
+      </c>
+      <c r="I175">
+        <v>196</v>
+      </c>
+      <c r="J175">
+        <v>1.9905633926391599</v>
+      </c>
+      <c r="K175">
+        <v>35.004123687744141</v>
+      </c>
+      <c r="L175">
+        <v>145.70661926269531</v>
+      </c>
+      <c r="M175">
+        <v>147.19142150878909</v>
+      </c>
+      <c r="N175">
+        <v>87</v>
+      </c>
+      <c r="O175">
+        <v>184</v>
+      </c>
+      <c r="P175">
+        <v>1.9841358661651609</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>190</v>
+      </c>
+      <c r="B176">
+        <v>15</v>
+      </c>
+      <c r="C176">
+        <v>0.36559140682220459</v>
+      </c>
+      <c r="D176">
+        <v>18.914913177490231</v>
+      </c>
+      <c r="E176">
+        <v>192</v>
+      </c>
+      <c r="F176">
+        <v>160</v>
+      </c>
+      <c r="G176">
+        <v>1.256006313636993</v>
+      </c>
+      <c r="H176">
+        <v>0.21176470816135409</v>
+      </c>
+      <c r="I176">
+        <v>202</v>
+      </c>
+      <c r="J176">
+        <v>2.7819609642028809</v>
+      </c>
+      <c r="K176">
+        <v>28.985956192016602</v>
+      </c>
+      <c r="L176">
+        <v>163.80888366699219</v>
+      </c>
+      <c r="M176">
+        <v>174.9359130859375</v>
+      </c>
+      <c r="N176">
+        <v>127</v>
+      </c>
+      <c r="O176">
+        <v>200</v>
+      </c>
+      <c r="P176">
+        <v>2.6076779365539551</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>191</v>
+      </c>
+      <c r="B177">
+        <v>15.6</v>
+      </c>
+      <c r="C177">
+        <v>0.37940379977226257</v>
+      </c>
+      <c r="D177">
+        <v>25.547161102294918</v>
+      </c>
+      <c r="E177">
+        <v>206</v>
+      </c>
+      <c r="F177">
+        <v>170</v>
+      </c>
+      <c r="G177">
+        <v>1.380156379783124</v>
+      </c>
+      <c r="H177">
+        <v>0.26666668057441711</v>
+      </c>
+      <c r="I177">
+        <v>211</v>
+      </c>
+      <c r="J177">
+        <v>2.8014175891876221</v>
+      </c>
+      <c r="K177">
+        <v>36.849796295166023</v>
+      </c>
+      <c r="L177">
+        <v>165.58738708496091</v>
+      </c>
+      <c r="M177">
+        <v>174.14208984375</v>
+      </c>
+      <c r="N177">
+        <v>114</v>
+      </c>
+      <c r="O177">
+        <v>210</v>
+      </c>
+      <c r="P177">
+        <v>2.355512380599976</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>192</v>
+      </c>
+      <c r="B178">
+        <v>15</v>
+      </c>
+      <c r="C178">
+        <v>0.38518518209457397</v>
+      </c>
+      <c r="D178">
+        <v>24.069316864013668</v>
+      </c>
+      <c r="E178">
+        <v>200</v>
+      </c>
+      <c r="F178">
+        <v>149</v>
+      </c>
+      <c r="G178">
+        <v>1.381247139825583</v>
+      </c>
+      <c r="H178">
+        <v>0.27843138575553888</v>
+      </c>
+      <c r="I178">
+        <v>198</v>
+      </c>
+      <c r="J178">
+        <v>3.3420710563659668</v>
+      </c>
+      <c r="K178">
+        <v>35.554473876953118</v>
+      </c>
+      <c r="L178">
+        <v>157.02900695800781</v>
+      </c>
+      <c r="M178">
+        <v>162.23973083496091</v>
+      </c>
+      <c r="N178">
+        <v>103</v>
+      </c>
+      <c r="O178">
+        <v>195</v>
+      </c>
+      <c r="P178">
+        <v>2.716183185577393</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>193</v>
+      </c>
+      <c r="B179">
+        <v>13</v>
+      </c>
+      <c r="C179">
+        <v>0.38533833622932429</v>
+      </c>
+      <c r="D179">
+        <v>24.069869995117191</v>
+      </c>
+      <c r="E179">
+        <v>202</v>
+      </c>
+      <c r="F179">
+        <v>154</v>
+      </c>
+      <c r="G179">
+        <v>1.3799206585913439</v>
+      </c>
+      <c r="H179">
+        <v>0.27843138575553888</v>
+      </c>
+      <c r="I179">
+        <v>208</v>
+      </c>
+      <c r="J179">
+        <v>2.7331511974334721</v>
+      </c>
+      <c r="K179">
+        <v>39.436111450195313</v>
+      </c>
+      <c r="L179">
+        <v>157.39985656738281</v>
+      </c>
+      <c r="M179">
+        <v>162.44647216796881</v>
+      </c>
+      <c r="N179">
+        <v>93</v>
+      </c>
+      <c r="O179">
+        <v>197</v>
+      </c>
+      <c r="P179">
+        <v>2.234538078308105</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>194</v>
+      </c>
+      <c r="B180">
+        <v>14.9</v>
+      </c>
+      <c r="C180">
+        <v>0.38208955526351929</v>
+      </c>
+      <c r="D180">
+        <v>21.899881362915039</v>
+      </c>
+      <c r="E180">
+        <v>195</v>
+      </c>
+      <c r="F180">
+        <v>154</v>
+      </c>
+      <c r="G180">
+        <v>1.3322824644967779</v>
+      </c>
+      <c r="H180">
+        <v>0.26666668057441711</v>
+      </c>
+      <c r="I180">
+        <v>212</v>
+      </c>
+      <c r="J180">
+        <v>2.224197626113892</v>
+      </c>
+      <c r="K180">
+        <v>37.446193695068359</v>
+      </c>
+      <c r="L180">
+        <v>158.99273681640619</v>
+      </c>
+      <c r="M180">
+        <v>164.39830017089841</v>
+      </c>
+      <c r="N180">
+        <v>100</v>
+      </c>
+      <c r="O180">
+        <v>199</v>
+      </c>
+      <c r="P180">
+        <v>2.091837882995605</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>195</v>
+      </c>
+      <c r="B181">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="C181">
+        <v>0.39457201957702642</v>
+      </c>
+      <c r="D181">
+        <v>28.334358215332031</v>
+      </c>
+      <c r="E181">
+        <v>195</v>
+      </c>
+      <c r="F181">
+        <v>168</v>
+      </c>
+      <c r="G181">
+        <v>1.4827921705859091</v>
+      </c>
+      <c r="H181">
+        <v>0.31764706969261169</v>
+      </c>
+      <c r="I181">
+        <v>188</v>
+      </c>
+      <c r="J181">
+        <v>2.6998238563537602</v>
+      </c>
+      <c r="K181">
+        <v>30.4770622253418</v>
+      </c>
+      <c r="L181">
+        <v>150.41375732421881</v>
+      </c>
+      <c r="M181">
+        <v>156.4085998535156</v>
+      </c>
+      <c r="N181">
+        <v>99</v>
+      </c>
+      <c r="O181">
+        <v>186</v>
+      </c>
+      <c r="P181">
+        <v>2.4527263641357422</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>196</v>
+      </c>
+      <c r="B182">
+        <v>13.8</v>
+      </c>
+      <c r="C182">
+        <v>0.41588786244392401</v>
+      </c>
+      <c r="D182">
+        <v>29.755178451538089</v>
+      </c>
+      <c r="E182">
+        <v>184</v>
+      </c>
+      <c r="F182">
+        <v>153</v>
+      </c>
+      <c r="G182">
+        <v>1.584496583423364</v>
+      </c>
+      <c r="H182">
+        <v>0.3803921639919281</v>
+      </c>
+      <c r="I182">
+        <v>187</v>
+      </c>
+      <c r="J182">
+        <v>2.3581175804138179</v>
+      </c>
+      <c r="K182">
+        <v>34.216083526611328</v>
+      </c>
+      <c r="L182">
+        <v>137.11302185058591</v>
+      </c>
+      <c r="M182">
+        <v>136.5146179199219</v>
+      </c>
+      <c r="N182">
+        <v>75</v>
+      </c>
+      <c r="O182">
+        <v>171</v>
+      </c>
+      <c r="P182">
+        <v>2.417370080947876</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>197</v>
+      </c>
+      <c r="B183">
+        <v>15.9</v>
+      </c>
+      <c r="C183">
+        <v>0.38530066609382629</v>
+      </c>
+      <c r="D183">
+        <v>28.70645904541016</v>
+      </c>
+      <c r="E183">
+        <v>198</v>
+      </c>
+      <c r="F183">
+        <v>169</v>
+      </c>
+      <c r="G183">
+        <v>1.4643043029012319</v>
+      </c>
+      <c r="H183">
+        <v>0.30196079611778259</v>
+      </c>
+      <c r="I183">
+        <v>191</v>
+      </c>
+      <c r="J183">
+        <v>2.9558181762695308</v>
+      </c>
+      <c r="K183">
+        <v>31.891448974609379</v>
+      </c>
+      <c r="L183">
+        <v>153.87469482421881</v>
+      </c>
+      <c r="M183">
+        <v>164.60707092285159</v>
+      </c>
+      <c r="N183">
+        <v>105</v>
+      </c>
+      <c r="O183">
+        <v>198</v>
+      </c>
+      <c r="P183">
+        <v>2.39207935333252</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>198</v>
+      </c>
+      <c r="B184">
+        <v>16.2</v>
+      </c>
+      <c r="C184">
+        <v>0.38223937153816218</v>
+      </c>
+      <c r="D184">
+        <v>25.392948150634769</v>
+      </c>
+      <c r="E184">
+        <v>193</v>
+      </c>
+      <c r="F184">
+        <v>152</v>
+      </c>
+      <c r="G184">
+        <v>1.387678089852217</v>
+      </c>
+      <c r="H184">
+        <v>0.29019609093666082</v>
+      </c>
+      <c r="I184">
+        <v>203</v>
+      </c>
+      <c r="J184">
+        <v>2.3393592834472661</v>
+      </c>
+      <c r="K184">
+        <v>33.140361785888672</v>
+      </c>
+      <c r="L184">
+        <v>154.14787292480469</v>
+      </c>
+      <c r="M184">
+        <v>166.75868225097659</v>
+      </c>
+      <c r="N184">
+        <v>112</v>
+      </c>
+      <c r="O184">
+        <v>196</v>
+      </c>
+      <c r="P184">
+        <v>2.3512759208679199</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>199</v>
+      </c>
+      <c r="B185">
+        <v>15.5</v>
+      </c>
+      <c r="C185">
+        <v>0.38386309146881098</v>
+      </c>
+      <c r="D185">
+        <v>26.608266830444339</v>
+      </c>
+      <c r="E185">
+        <v>184</v>
+      </c>
+      <c r="F185">
+        <v>151</v>
+      </c>
+      <c r="G185">
+        <v>1.457845228402193</v>
+      </c>
+      <c r="H185">
+        <v>0.29019609093666082</v>
+      </c>
+      <c r="I185">
+        <v>175</v>
+      </c>
+      <c r="J185">
+        <v>3.20001220703125</v>
+      </c>
+      <c r="K185">
+        <v>28.804193496704102</v>
+      </c>
+      <c r="L185">
+        <v>142.86027526855469</v>
+      </c>
+      <c r="M185">
+        <v>152.23497009277341</v>
+      </c>
+      <c r="N185">
+        <v>93</v>
+      </c>
+      <c r="O185">
+        <v>180</v>
+      </c>
+      <c r="P185">
+        <v>2.8189558982849121</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>200</v>
+      </c>
+      <c r="B186">
+        <v>14.1</v>
+      </c>
+      <c r="C186">
+        <v>0.38311687111854548</v>
+      </c>
+      <c r="D186">
+        <v>23.241048812866211</v>
+      </c>
+      <c r="E186">
+        <v>202</v>
+      </c>
+      <c r="F186">
+        <v>174</v>
+      </c>
+      <c r="G186">
+        <v>1.349612305185649</v>
+      </c>
+      <c r="H186">
+        <v>0.26274511218070978</v>
+      </c>
+      <c r="I186">
+        <v>210</v>
+      </c>
+      <c r="J186">
+        <v>2.894633531570435</v>
+      </c>
+      <c r="K186">
+        <v>34.527275085449219</v>
+      </c>
+      <c r="L186">
+        <v>164.3390197753906</v>
+      </c>
+      <c r="M186">
+        <v>169.18647766113281</v>
+      </c>
+      <c r="N186">
+        <v>107</v>
+      </c>
+      <c r="O186">
+        <v>202</v>
+      </c>
+      <c r="P186">
+        <v>2.5420157909393311</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>201</v>
+      </c>
+      <c r="B187">
+        <v>12</v>
+      </c>
+      <c r="C187">
+        <v>0.35363790392875671</v>
+      </c>
+      <c r="D187">
+        <v>14.887014389038089</v>
+      </c>
+      <c r="E187">
+        <v>193</v>
+      </c>
+      <c r="F187">
+        <v>170</v>
+      </c>
+      <c r="G187">
+        <v>1.1774724471428419</v>
+      </c>
+      <c r="H187">
+        <v>0.16078431904315951</v>
+      </c>
+      <c r="I187">
+        <v>212</v>
+      </c>
+      <c r="J187">
+        <v>1.9450159072875981</v>
+      </c>
+      <c r="K187">
+        <v>32.985065460205078</v>
+      </c>
+      <c r="L187">
+        <v>174.0622253417969</v>
+      </c>
+      <c r="M187">
+        <v>184.30607604980469</v>
+      </c>
+      <c r="N187">
+        <v>125</v>
+      </c>
+      <c r="O187">
+        <v>222</v>
+      </c>
+      <c r="P187">
+        <v>1.9291757345199581</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>202</v>
+      </c>
+      <c r="B188">
+        <v>15.3</v>
+      </c>
+      <c r="C188">
+        <v>0.40317460894584661</v>
+      </c>
+      <c r="D188">
+        <v>27.872356414794918</v>
+      </c>
+      <c r="E188">
+        <v>199</v>
+      </c>
+      <c r="F188">
+        <v>176</v>
+      </c>
+      <c r="G188">
+        <v>1.485931449716021</v>
+      </c>
+      <c r="H188">
+        <v>0.31764706969261169</v>
+      </c>
+      <c r="I188">
+        <v>211</v>
+      </c>
+      <c r="J188">
+        <v>1.557840943336487</v>
+      </c>
+      <c r="K188">
+        <v>43.782722473144531</v>
+      </c>
+      <c r="L188">
+        <v>154.1528015136719</v>
+      </c>
+      <c r="M188">
+        <v>149.82440185546881</v>
+      </c>
+      <c r="N188">
+        <v>72</v>
+      </c>
+      <c r="O188">
+        <v>208</v>
+      </c>
+      <c r="P188">
+        <v>1.5225216150283809</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>203</v>
+      </c>
+      <c r="B189">
+        <v>13.7</v>
+      </c>
+      <c r="C189">
+        <v>0.40816327929496771</v>
+      </c>
+      <c r="D189">
+        <v>27.91140174865723</v>
+      </c>
+      <c r="E189">
+        <v>189</v>
+      </c>
+      <c r="F189">
+        <v>162</v>
+      </c>
+      <c r="G189">
+        <v>1.5217046809378829</v>
+      </c>
+      <c r="H189">
+        <v>0.33725491166114813</v>
+      </c>
+      <c r="I189">
+        <v>205</v>
+      </c>
+      <c r="J189">
+        <v>1.906749486923218</v>
+      </c>
+      <c r="K189">
+        <v>41.570720672607422</v>
+      </c>
+      <c r="L189">
+        <v>144.271484375</v>
+      </c>
+      <c r="M189">
+        <v>140.3893737792969</v>
+      </c>
+      <c r="N189">
+        <v>70</v>
+      </c>
+      <c r="O189">
+        <v>189</v>
+      </c>
+      <c r="P189">
+        <v>1.8359746932983401</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>204</v>
+      </c>
+      <c r="B190">
+        <v>13.4</v>
+      </c>
+      <c r="C190">
+        <v>0.42231947183609009</v>
+      </c>
+      <c r="D190">
+        <v>30.97480583190918</v>
+      </c>
+      <c r="E190">
+        <v>199</v>
+      </c>
+      <c r="F190">
+        <v>177</v>
+      </c>
+      <c r="G190">
+        <v>1.5848390981922691</v>
+      </c>
+      <c r="H190">
+        <v>0.37254902720451349</v>
+      </c>
+      <c r="I190">
+        <v>190</v>
+      </c>
+      <c r="J190">
+        <v>2.1707956790924068</v>
+      </c>
+      <c r="K190">
+        <v>32.185802459716797</v>
+      </c>
+      <c r="L190">
+        <v>148.41419982910159</v>
+      </c>
+      <c r="M190">
+        <v>142.70610046386719</v>
+      </c>
+      <c r="N190">
+        <v>79</v>
+      </c>
+      <c r="O190">
+        <v>180</v>
+      </c>
+      <c r="P190">
+        <v>2.115007877349854</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>205</v>
+      </c>
+      <c r="B191">
+        <v>12.3</v>
+      </c>
+      <c r="C191">
+        <v>0.36741766333580023</v>
+      </c>
+      <c r="D191">
+        <v>21.312627792358398</v>
+      </c>
+      <c r="E191">
+        <v>201</v>
+      </c>
+      <c r="F191">
+        <v>172</v>
+      </c>
+      <c r="G191">
+        <v>1.300896233601575</v>
+      </c>
+      <c r="H191">
+        <v>0.21960784494876859</v>
+      </c>
+      <c r="I191">
+        <v>220</v>
+      </c>
+      <c r="J191">
+        <v>1.8051682710647581</v>
+      </c>
+      <c r="K191">
+        <v>36.747077941894531</v>
+      </c>
+      <c r="L191">
+        <v>167.5662841796875</v>
+      </c>
+      <c r="M191">
+        <v>172.96977233886719</v>
+      </c>
+      <c r="N191">
+        <v>101</v>
+      </c>
+      <c r="O191">
+        <v>217</v>
+      </c>
+      <c r="P191">
+        <v>1.861825108528137</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>206</v>
+      </c>
+      <c r="B192">
+        <v>12.9</v>
+      </c>
+      <c r="C192">
+        <v>0.40062111616134638</v>
+      </c>
+      <c r="D192">
+        <v>26.27456092834473</v>
+      </c>
+      <c r="E192">
+        <v>193</v>
+      </c>
+      <c r="F192">
+        <v>141</v>
+      </c>
+      <c r="G192">
+        <v>1.4818222360957229</v>
+      </c>
+      <c r="H192">
+        <v>0.30980393290519709</v>
+      </c>
+      <c r="I192">
+        <v>190</v>
+      </c>
+      <c r="J192">
+        <v>2.3216569423675542</v>
+      </c>
+      <c r="K192">
+        <v>36.424285888671882</v>
+      </c>
+      <c r="L192">
+        <v>143.9951171875</v>
+      </c>
+      <c r="M192">
+        <v>142.70887756347659</v>
+      </c>
+      <c r="N192">
+        <v>80</v>
+      </c>
+      <c r="O192">
+        <v>181</v>
+      </c>
+      <c r="P192">
+        <v>1.9929960966110229</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>207</v>
+      </c>
+      <c r="B193">
+        <v>13.5</v>
+      </c>
+      <c r="C193">
+        <v>0.36774194240570068</v>
+      </c>
+      <c r="D193">
+        <v>18.80606651306152</v>
+      </c>
+      <c r="E193">
+        <v>191</v>
+      </c>
+      <c r="F193">
+        <v>138</v>
+      </c>
+      <c r="G193">
+        <v>1.2668928050356361</v>
+      </c>
+      <c r="H193">
+        <v>0.21568627655506131</v>
+      </c>
+      <c r="I193">
+        <v>215</v>
+      </c>
+      <c r="J193">
+        <v>1.95127260684967</v>
+      </c>
+      <c r="K193">
+        <v>44.045036315917969</v>
+      </c>
+      <c r="L193">
+        <v>157.42999267578119</v>
+      </c>
+      <c r="M193">
+        <v>164.9443664550781</v>
+      </c>
+      <c r="N193">
+        <v>89</v>
+      </c>
+      <c r="O193">
+        <v>216</v>
+      </c>
+      <c r="P193">
+        <v>1.8465176820755</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>208</v>
+      </c>
+      <c r="B194">
+        <v>13.7</v>
+      </c>
+      <c r="C194">
+        <v>0.38579654693603521</v>
+      </c>
+      <c r="D194">
+        <v>24.631698608398441</v>
+      </c>
+      <c r="E194">
+        <v>187</v>
+      </c>
+      <c r="F194">
+        <v>158</v>
+      </c>
+      <c r="G194">
+        <v>1.410862497335017</v>
+      </c>
+      <c r="H194">
+        <v>0.27843138575553888</v>
+      </c>
+      <c r="I194">
+        <v>205</v>
+      </c>
+      <c r="J194">
+        <v>1.8869786262512209</v>
+      </c>
+      <c r="K194">
+        <v>39.505348205566413</v>
+      </c>
+      <c r="L194">
+        <v>149.0213928222656</v>
+      </c>
+      <c r="M194">
+        <v>151.24632263183591</v>
+      </c>
+      <c r="N194">
+        <v>71</v>
+      </c>
+      <c r="O194">
+        <v>196</v>
+      </c>
+      <c r="P194">
+        <v>1.884158253669739</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>209</v>
+      </c>
+      <c r="B195">
+        <v>16.8</v>
+      </c>
+      <c r="C195">
+        <v>0.39300411939620972</v>
+      </c>
+      <c r="D195">
+        <v>25.233028411865231</v>
+      </c>
+      <c r="E195">
+        <v>199</v>
+      </c>
+      <c r="F195">
+        <v>158</v>
+      </c>
+      <c r="G195">
+        <v>1.4218664886205981</v>
+      </c>
+      <c r="H195">
+        <v>0.29019609093666082</v>
+      </c>
+      <c r="I195">
+        <v>204</v>
+      </c>
+      <c r="J195">
+        <v>2.8892335891723628</v>
+      </c>
+      <c r="K195">
+        <v>39.625003814697273</v>
+      </c>
+      <c r="L195">
+        <v>153.9735107421875</v>
+      </c>
+      <c r="M195">
+        <v>155.59468078613281</v>
+      </c>
+      <c r="N195">
+        <v>81</v>
+      </c>
+      <c r="O195">
+        <v>190</v>
+      </c>
+      <c r="P195">
+        <v>2.4494543075561519</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>210</v>
+      </c>
+      <c r="B196">
+        <v>15.4</v>
+      </c>
+      <c r="C196">
+        <v>0.40782123804092407</v>
+      </c>
+      <c r="D196">
+        <v>28.69630241394043</v>
+      </c>
+      <c r="E196">
+        <v>183</v>
+      </c>
+      <c r="F196">
+        <v>144</v>
+      </c>
+      <c r="G196">
+        <v>1.541052252431879</v>
+      </c>
+      <c r="H196">
+        <v>0.35294118523597717</v>
+      </c>
+      <c r="I196">
+        <v>204</v>
+      </c>
+      <c r="J196">
+        <v>1.8947408199310301</v>
+      </c>
+      <c r="K196">
+        <v>43.745491027832031</v>
+      </c>
+      <c r="L196">
+        <v>138.96641540527341</v>
+      </c>
+      <c r="M196">
+        <v>141.23417663574219</v>
+      </c>
+      <c r="N196">
+        <v>64</v>
+      </c>
+      <c r="O196">
+        <v>190</v>
+      </c>
+      <c r="P196">
+        <v>1.867439746856689</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>211</v>
+      </c>
+      <c r="B197">
+        <v>14.7</v>
+      </c>
+      <c r="C197">
+        <v>0.37809917330741882</v>
+      </c>
+      <c r="D197">
+        <v>22.855100631713871</v>
+      </c>
+      <c r="E197">
+        <v>190</v>
+      </c>
+      <c r="F197">
+        <v>145</v>
+      </c>
+      <c r="G197">
+        <v>1.3466774566040061</v>
+      </c>
+      <c r="H197">
+        <v>0.26274511218070978</v>
+      </c>
+      <c r="I197">
+        <v>212</v>
+      </c>
+      <c r="J197">
+        <v>2.116757869720459</v>
+      </c>
+      <c r="K197">
+        <v>45.983524322509773</v>
+      </c>
+      <c r="L197">
+        <v>154.29936218261719</v>
+      </c>
+      <c r="M197">
+        <v>162.95140075683591</v>
+      </c>
+      <c r="N197">
+        <v>78</v>
+      </c>
+      <c r="O197">
+        <v>213</v>
+      </c>
+      <c r="P197">
+        <v>1.8628109693527219</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>212</v>
+      </c>
+      <c r="B198">
+        <v>14.3</v>
+      </c>
+      <c r="C198">
+        <v>0.40920096635818481</v>
+      </c>
+      <c r="D198">
+        <v>25.63519287109375</v>
+      </c>
+      <c r="E198">
+        <v>183</v>
+      </c>
+      <c r="F198">
+        <v>164</v>
+      </c>
+      <c r="G198">
+        <v>1.472243859890171</v>
+      </c>
+      <c r="H198">
+        <v>0.3333333432674408</v>
+      </c>
+      <c r="I198">
+        <v>174</v>
+      </c>
+      <c r="J198">
+        <v>4.5170612335205078</v>
+      </c>
+      <c r="K198">
+        <v>23.9613151550293</v>
+      </c>
+      <c r="L198">
+        <v>142.77952575683591</v>
+      </c>
+      <c r="M198">
+        <v>141.99479675292969</v>
+      </c>
+      <c r="N198">
+        <v>104</v>
+      </c>
+      <c r="O198">
+        <v>162</v>
+      </c>
+      <c r="P198">
+        <v>4.1668415069580078</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>213</v>
+      </c>
+      <c r="B199">
+        <v>13.5</v>
+      </c>
+      <c r="C199">
+        <v>0.41780820488929749</v>
+      </c>
+      <c r="D199">
+        <v>26.978157043457031</v>
+      </c>
+      <c r="E199">
+        <v>183</v>
+      </c>
+      <c r="F199">
+        <v>157</v>
+      </c>
+      <c r="G199">
+        <v>1.529703665773448</v>
+      </c>
+      <c r="H199">
+        <v>0.34509804844856262</v>
+      </c>
+      <c r="I199">
+        <v>178</v>
+      </c>
+      <c r="J199">
+        <v>2.384699821472168</v>
+      </c>
+      <c r="K199">
+        <v>31.374626159667969</v>
+      </c>
+      <c r="L199">
+        <v>138.67567443847659</v>
+      </c>
+      <c r="M199">
+        <v>132.94325256347659</v>
+      </c>
+      <c r="N199">
+        <v>81</v>
+      </c>
+      <c r="O199">
+        <v>167</v>
+      </c>
+      <c r="P199">
+        <v>2.3245422840118408</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>214</v>
+      </c>
+      <c r="B200">
+        <v>15.6</v>
+      </c>
+      <c r="C200">
+        <v>0.41164657473564148</v>
+      </c>
+      <c r="D200">
+        <v>29.464740753173832</v>
+      </c>
+      <c r="E200">
+        <v>191</v>
+      </c>
+      <c r="F200">
+        <v>158</v>
+      </c>
+      <c r="G200">
+        <v>1.5646215765952629</v>
+      </c>
+      <c r="H200">
+        <v>0.35294118523597717</v>
+      </c>
+      <c r="I200">
+        <v>175</v>
+      </c>
+      <c r="J200">
+        <v>2.5675520896911621</v>
+      </c>
+      <c r="K200">
+        <v>27.36948394775391</v>
+      </c>
+      <c r="L200">
+        <v>141.20660400390619</v>
+      </c>
+      <c r="M200">
+        <v>140.56010437011719</v>
+      </c>
+      <c r="N200">
+        <v>91</v>
+      </c>
+      <c r="O200">
+        <v>170</v>
+      </c>
+      <c r="P200">
+        <v>2.581853866577148</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>215</v>
+      </c>
+      <c r="B201">
+        <v>14.8</v>
+      </c>
+      <c r="C201">
+        <v>0.37309643626213068</v>
+      </c>
+      <c r="D201">
+        <v>22.42131233215332</v>
+      </c>
+      <c r="E201">
+        <v>182</v>
+      </c>
+      <c r="F201">
+        <v>123</v>
+      </c>
+      <c r="G201">
+        <v>1.362304242931716</v>
+      </c>
+      <c r="H201">
+        <v>0.25490197539329529</v>
+      </c>
+      <c r="I201">
+        <v>208</v>
+      </c>
+      <c r="J201">
+        <v>1.793432831764221</v>
+      </c>
+      <c r="K201">
+        <v>48.915924072265618</v>
+      </c>
+      <c r="L201">
+        <v>144.84535217285159</v>
+      </c>
+      <c r="M201">
+        <v>151.81996154785159</v>
+      </c>
+      <c r="N201">
+        <v>69</v>
+      </c>
+      <c r="O201">
+        <v>209</v>
+      </c>
+      <c r="P201">
+        <v>1.6993821859359739</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>216</v>
+      </c>
+      <c r="B202">
+        <v>14.8</v>
+      </c>
+      <c r="C202">
+        <v>0.40211638808250427</v>
+      </c>
+      <c r="D202">
+        <v>26.86655235290527</v>
+      </c>
+      <c r="E202">
+        <v>181</v>
+      </c>
+      <c r="F202">
+        <v>149</v>
+      </c>
+      <c r="G202">
+        <v>1.489930621933494</v>
+      </c>
+      <c r="H202">
+        <v>0.32941177487373352</v>
+      </c>
+      <c r="I202">
+        <v>194</v>
+      </c>
+      <c r="J202">
+        <v>2.104164838790894</v>
+      </c>
+      <c r="K202">
+        <v>36.294403076171882</v>
+      </c>
+      <c r="L202">
+        <v>139.62748718261719</v>
+      </c>
+      <c r="M202">
+        <v>143.78228759765619</v>
+      </c>
+      <c r="N202">
+        <v>84</v>
+      </c>
+      <c r="O202">
+        <v>183</v>
+      </c>
+      <c r="P202">
+        <v>1.976390480995178</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>217</v>
+      </c>
+      <c r="B203">
+        <v>14.9</v>
+      </c>
+      <c r="C203">
+        <v>0.38086304068565369</v>
+      </c>
+      <c r="D203">
+        <v>24.679855346679691</v>
+      </c>
+      <c r="E203">
+        <v>196</v>
+      </c>
+      <c r="F203">
+        <v>159</v>
+      </c>
+      <c r="G203">
+        <v>1.3709220263037949</v>
+      </c>
+      <c r="H203">
+        <v>0.27843138575553888</v>
+      </c>
+      <c r="I203">
+        <v>207</v>
+      </c>
+      <c r="J203">
+        <v>2.4446206092834468</v>
+      </c>
+      <c r="K203">
+        <v>36.861377716064453</v>
+      </c>
+      <c r="L203">
+        <v>157.61846923828119</v>
+      </c>
+      <c r="M203">
+        <v>168.70758056640619</v>
+      </c>
+      <c r="N203">
+        <v>104</v>
+      </c>
+      <c r="O203">
+        <v>203</v>
+      </c>
+      <c r="P203">
+        <v>2.2684686183929439</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>218</v>
+      </c>
+      <c r="B204">
+        <v>12.4</v>
+      </c>
+      <c r="C204">
+        <v>0.38065844774246221</v>
+      </c>
+      <c r="D204">
+        <v>22.3840217590332</v>
+      </c>
+      <c r="E204">
+        <v>188</v>
+      </c>
+      <c r="F204">
+        <v>134</v>
+      </c>
+      <c r="G204">
+        <v>1.352740320860959</v>
+      </c>
+      <c r="H204">
+        <v>0.27450981736183172</v>
+      </c>
+      <c r="I204">
+        <v>200</v>
+      </c>
+      <c r="J204">
+        <v>2.9507133960723881</v>
+      </c>
+      <c r="K204">
+        <v>37.9407958984375</v>
+      </c>
+      <c r="L204">
+        <v>149.68739318847659</v>
+      </c>
+      <c r="M204">
+        <v>158.43263244628909</v>
+      </c>
+      <c r="N204">
+        <v>94</v>
+      </c>
+      <c r="O204">
+        <v>190</v>
+      </c>
+      <c r="P204">
+        <v>2.3966012001037602</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>219</v>
+      </c>
+      <c r="B205">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="C205">
+        <v>0.40530303120613098</v>
+      </c>
+      <c r="D205">
+        <v>27.243740081787109</v>
+      </c>
+      <c r="E205">
+        <v>196</v>
+      </c>
+      <c r="F205">
+        <v>149</v>
+      </c>
+      <c r="G205">
+        <v>1.4954745013963631</v>
+      </c>
+      <c r="H205">
+        <v>0.32549020648002619</v>
+      </c>
+      <c r="I205">
+        <v>180</v>
+      </c>
+      <c r="J205">
+        <v>2.7869381904602051</v>
+      </c>
+      <c r="K205">
+        <v>29.577409744262699</v>
+      </c>
+      <c r="L205">
+        <v>146.67878723144531</v>
+      </c>
+      <c r="M205">
+        <v>146.05998229980469</v>
+      </c>
+      <c r="N205">
+        <v>92</v>
+      </c>
+      <c r="O205">
+        <v>171</v>
+      </c>
+      <c r="P205">
+        <v>2.522422075271606</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>220</v>
+      </c>
+      <c r="B206">
+        <v>15.6</v>
+      </c>
+      <c r="C206">
+        <v>0.45386534929275513</v>
+      </c>
+      <c r="D206">
+        <v>32.4239501953125</v>
+      </c>
+      <c r="E206">
+        <v>200</v>
+      </c>
+      <c r="F206">
+        <v>164</v>
+      </c>
+      <c r="G206">
+        <v>1.70720619025664</v>
+      </c>
+      <c r="H206">
+        <v>0.42352941632270807</v>
+      </c>
+      <c r="I206">
+        <v>176</v>
+      </c>
+      <c r="J206">
+        <v>3.496296882629395</v>
+      </c>
+      <c r="K206">
+        <v>28.230531692504879</v>
+      </c>
+      <c r="L206">
+        <v>138.30134582519531</v>
+      </c>
+      <c r="M206">
+        <v>117.23597717285161</v>
+      </c>
+      <c r="N206">
+        <v>64</v>
+      </c>
+      <c r="O206">
+        <v>146</v>
+      </c>
+      <c r="P206">
+        <v>3.3484797477722168</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>221</v>
+      </c>
+      <c r="B207">
+        <v>13.7</v>
+      </c>
+      <c r="C207">
+        <v>0.3617977499961853</v>
+      </c>
+      <c r="D207">
+        <v>19.489559173583981</v>
+      </c>
+      <c r="E207">
+        <v>182</v>
+      </c>
+      <c r="F207">
+        <v>146</v>
+      </c>
+      <c r="G207">
+        <v>1.270724511370712</v>
+      </c>
+      <c r="H207">
+        <v>0.21568627655506131</v>
+      </c>
+      <c r="I207">
+        <v>212</v>
+      </c>
+      <c r="J207">
+        <v>1.9822483062744141</v>
+      </c>
+      <c r="K207">
+        <v>44.140106201171882</v>
+      </c>
+      <c r="L207">
+        <v>155.7114562988281</v>
+      </c>
+      <c r="M207">
+        <v>166.73313903808591</v>
+      </c>
+      <c r="N207">
+        <v>88</v>
+      </c>
+      <c r="O207">
+        <v>221</v>
+      </c>
+      <c r="P207">
+        <v>1.799760580062866</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>222</v>
+      </c>
+      <c r="B208">
+        <v>15.4</v>
+      </c>
+      <c r="C208">
+        <v>0.36475411057472229</v>
+      </c>
+      <c r="D208">
+        <v>20.715530395507809</v>
+      </c>
+      <c r="E208">
+        <v>196</v>
+      </c>
+      <c r="F208">
+        <v>167</v>
+      </c>
+      <c r="G208">
+        <v>1.2826160684638801</v>
+      </c>
+      <c r="H208">
+        <v>0.20784313976764679</v>
+      </c>
+      <c r="I208">
+        <v>211</v>
+      </c>
+      <c r="J208">
+        <v>2.5035924911499019</v>
+      </c>
+      <c r="K208">
+        <v>35.600521087646477</v>
+      </c>
+      <c r="L208">
+        <v>165.28089904785159</v>
+      </c>
+      <c r="M208">
+        <v>175.3785705566406</v>
+      </c>
+      <c r="N208">
+        <v>105</v>
+      </c>
+      <c r="O208">
+        <v>219</v>
+      </c>
+      <c r="P208">
+        <v>2.3604907989501949</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>223</v>
+      </c>
+      <c r="B209">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="C209">
+        <v>0.36654135584831238</v>
+      </c>
+      <c r="D209">
+        <v>13.70323276519775</v>
+      </c>
+      <c r="E209">
+        <v>183</v>
+      </c>
+      <c r="F209">
+        <v>128</v>
+      </c>
+      <c r="G209">
+        <v>1.1912468884299141</v>
+      </c>
+      <c r="H209">
+        <v>0.20392157137393949</v>
+      </c>
+      <c r="I209">
+        <v>208</v>
+      </c>
+      <c r="J209">
+        <v>2.2312970161437988</v>
+      </c>
+      <c r="K209">
+        <v>39.159210205078118</v>
+      </c>
+      <c r="L209">
+        <v>155.7696838378906</v>
+      </c>
+      <c r="M209">
+        <v>160.8351135253906</v>
+      </c>
+      <c r="N209">
+        <v>99</v>
+      </c>
+      <c r="O209">
+        <v>199</v>
+      </c>
+      <c r="P209">
+        <v>1.942379236221313</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>224</v>
+      </c>
+      <c r="B210">
+        <v>13</v>
+      </c>
+      <c r="C210">
+        <v>0.39344263076782232</v>
+      </c>
+      <c r="D210">
+        <v>23.10604286193848</v>
+      </c>
+      <c r="E210">
+        <v>188</v>
+      </c>
+      <c r="F210">
+        <v>152</v>
+      </c>
+      <c r="G210">
+        <v>1.360970582262067</v>
+      </c>
+      <c r="H210">
+        <v>0.29803922772407532</v>
+      </c>
+      <c r="I210">
+        <v>216</v>
+      </c>
+      <c r="J210">
+        <v>2.2219669818878169</v>
+      </c>
+      <c r="K210">
+        <v>41.556964874267578</v>
+      </c>
+      <c r="L210">
+        <v>153.54609680175781</v>
+      </c>
+      <c r="M210">
+        <v>159.52217102050781</v>
+      </c>
+      <c r="N210">
+        <v>97</v>
+      </c>
+      <c r="O210">
+        <v>208</v>
+      </c>
+      <c r="P210">
+        <v>1.997974634170532</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>225</v>
+      </c>
+      <c r="B211">
+        <v>15.4</v>
+      </c>
+      <c r="C211">
+        <v>0.38841202855110168</v>
+      </c>
+      <c r="D211">
+        <v>25.652240753173832</v>
+      </c>
+      <c r="E211">
+        <v>188</v>
+      </c>
+      <c r="F211">
+        <v>153</v>
+      </c>
+      <c r="G211">
+        <v>1.428014829928332</v>
+      </c>
+      <c r="H211">
+        <v>0.29019609093666082</v>
+      </c>
+      <c r="I211">
+        <v>194</v>
+      </c>
+      <c r="J211">
+        <v>2.261658668518066</v>
+      </c>
+      <c r="K211">
+        <v>32.64056396484375</v>
+      </c>
+      <c r="L211">
+        <v>148.92707824707031</v>
+      </c>
+      <c r="M211">
+        <v>155.57560729980469</v>
+      </c>
+      <c r="N211">
+        <v>98</v>
+      </c>
+      <c r="O211">
+        <v>185</v>
+      </c>
+      <c r="P211">
+        <v>2.2339892387390141</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>226</v>
+      </c>
+      <c r="B212">
+        <v>12.3</v>
+      </c>
+      <c r="C212">
+        <v>0.38579654693603521</v>
+      </c>
+      <c r="D212">
+        <v>24.725400924682621</v>
+      </c>
+      <c r="E212">
+        <v>195</v>
+      </c>
+      <c r="F212">
+        <v>162</v>
+      </c>
+      <c r="G212">
+        <v>1.3884802741868449</v>
+      </c>
+      <c r="H212">
+        <v>0.27450981736183172</v>
+      </c>
+      <c r="I212">
+        <v>198</v>
+      </c>
+      <c r="J212">
+        <v>2.803366899490356</v>
+      </c>
+      <c r="K212">
+        <v>31.258518218994141</v>
+      </c>
+      <c r="L212">
+        <v>155.9021301269531</v>
+      </c>
+      <c r="M212">
+        <v>163.1720275878906</v>
+      </c>
+      <c r="N212">
+        <v>112</v>
+      </c>
+      <c r="O212">
+        <v>192</v>
+      </c>
+      <c r="P212">
+        <v>2.6202692985534668</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>227</v>
+      </c>
+      <c r="B213">
+        <v>15.2</v>
+      </c>
+      <c r="C213">
+        <v>0.386892169713974</v>
+      </c>
+      <c r="D213">
+        <v>23.010623931884769</v>
+      </c>
+      <c r="E213">
+        <v>185</v>
+      </c>
+      <c r="F213">
+        <v>155</v>
+      </c>
+      <c r="G213">
+        <v>1.3781123729554889</v>
+      </c>
+      <c r="H213">
+        <v>0.27450981736183172</v>
+      </c>
+      <c r="I213">
+        <v>194</v>
+      </c>
+      <c r="J213">
+        <v>2.0251719951629639</v>
+      </c>
+      <c r="K213">
+        <v>33.923904418945313</v>
+      </c>
+      <c r="L213">
+        <v>148.48077392578119</v>
+      </c>
+      <c r="M213">
+        <v>153.47715759277341</v>
+      </c>
+      <c r="N213">
+        <v>89</v>
+      </c>
+      <c r="O213">
+        <v>190</v>
+      </c>
+      <c r="P213">
+        <v>2.0194847583770752</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>228</v>
+      </c>
+      <c r="B214">
+        <v>13.8</v>
+      </c>
+      <c r="C214">
+        <v>0.39557740092277532</v>
+      </c>
+      <c r="D214">
+        <v>25.786928176879879</v>
+      </c>
+      <c r="E214">
+        <v>195</v>
+      </c>
+      <c r="F214">
+        <v>162</v>
+      </c>
+      <c r="G214">
+        <v>1.4285557752546429</v>
+      </c>
+      <c r="H214">
+        <v>0.30588236451148992</v>
+      </c>
+      <c r="I214">
+        <v>200</v>
+      </c>
+      <c r="J214">
+        <v>2.4989795684814449</v>
+      </c>
+      <c r="K214">
+        <v>32.433280944824219</v>
+      </c>
+      <c r="L214">
+        <v>153.62542724609381</v>
+      </c>
+      <c r="M214">
+        <v>157.45733642578119</v>
+      </c>
+      <c r="N214">
+        <v>107</v>
+      </c>
+      <c r="O214">
+        <v>188</v>
+      </c>
+      <c r="P214">
+        <v>2.445165634155273</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>229</v>
+      </c>
+      <c r="B215">
+        <v>14.7</v>
+      </c>
+      <c r="C215">
+        <v>0.42888888716697687</v>
+      </c>
+      <c r="D215">
+        <v>31.752092361450199</v>
+      </c>
+      <c r="E215">
+        <v>197</v>
+      </c>
+      <c r="F215">
+        <v>171</v>
+      </c>
+      <c r="G215">
+        <v>1.630406886439639</v>
+      </c>
+      <c r="H215">
+        <v>0.38431373238563538</v>
+      </c>
+      <c r="I215">
+        <v>180</v>
+      </c>
+      <c r="J215">
+        <v>2.6412391662597661</v>
+      </c>
+      <c r="K215">
+        <v>29.1689338684082</v>
+      </c>
+      <c r="L215">
+        <v>142.8977355957031</v>
+      </c>
+      <c r="M215">
+        <v>136.53092956542969</v>
+      </c>
+      <c r="N215">
+        <v>86</v>
+      </c>
+      <c r="O215">
+        <v>167</v>
+      </c>
+      <c r="P215">
+        <v>2.499730110168457</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>230</v>
+      </c>
+      <c r="B216">
+        <v>15.1</v>
+      </c>
+      <c r="C216">
+        <v>0.37572255730628967</v>
+      </c>
+      <c r="D216">
+        <v>21.24176025390625</v>
+      </c>
+      <c r="E216">
+        <v>193</v>
+      </c>
+      <c r="F216">
+        <v>150</v>
+      </c>
+      <c r="G216">
+        <v>1.30457768074617</v>
+      </c>
+      <c r="H216">
+        <v>0.25490197539329529</v>
+      </c>
+      <c r="I216">
+        <v>208</v>
+      </c>
+      <c r="J216">
+        <v>2.3152287006378169</v>
+      </c>
+      <c r="K216">
+        <v>36.207836151123047</v>
+      </c>
+      <c r="L216">
+        <v>158.5896911621094</v>
+      </c>
+      <c r="M216">
+        <v>168.76707458496091</v>
+      </c>
+      <c r="N216">
+        <v>106</v>
+      </c>
+      <c r="O216">
+        <v>207</v>
+      </c>
+      <c r="P216">
+        <v>2.0614430904388432</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>231</v>
+      </c>
+      <c r="B217">
+        <v>15.2</v>
+      </c>
+      <c r="C217">
+        <v>0.39747634530067438</v>
+      </c>
+      <c r="D217">
+        <v>28.7714958190918</v>
+      </c>
+      <c r="E217">
+        <v>196</v>
+      </c>
+      <c r="F217">
+        <v>166</v>
+      </c>
+      <c r="G217">
+        <v>1.507987622526157</v>
+      </c>
+      <c r="H217">
+        <v>0.32156863808631903</v>
+      </c>
+      <c r="I217">
+        <v>192</v>
+      </c>
+      <c r="J217">
+        <v>2.7258157730102539</v>
+      </c>
+      <c r="K217">
+        <v>34.550453186035163</v>
+      </c>
+      <c r="L217">
+        <v>148.827880859375</v>
+      </c>
+      <c r="M217">
+        <v>151.88177490234381</v>
+      </c>
+      <c r="N217">
+        <v>91</v>
+      </c>
+      <c r="O217">
+        <v>184</v>
+      </c>
+      <c r="P217">
+        <v>2.3145232200622559</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>232</v>
+      </c>
+      <c r="B218">
+        <v>15.5</v>
+      </c>
+      <c r="C218">
+        <v>0.37556561827659612</v>
+      </c>
+      <c r="D218">
+        <v>20.871810913085941</v>
+      </c>
+      <c r="E218">
+        <v>193</v>
+      </c>
+      <c r="F218">
+        <v>159</v>
+      </c>
+      <c r="G218">
+        <v>1.321825264096262</v>
+      </c>
+      <c r="H218">
+        <v>0.23529411852359769</v>
+      </c>
+      <c r="I218">
+        <v>211</v>
+      </c>
+      <c r="J218">
         <v>2.150527715682983</v>
       </c>
-      <c r="K150">
+      <c r="K218">
         <v>39.542560577392578</v>
       </c>
-      <c r="L150">
+      <c r="L218">
         <v>158.15711975097659</v>
       </c>
-      <c r="M150">
+      <c r="M218">
         <v>160.80506896972659</v>
       </c>
-      <c r="N150">
+      <c r="N218">
         <v>88</v>
       </c>
-      <c r="O150">
+      <c r="O218">
         <v>198</v>
       </c>
-      <c r="P150">
+      <c r="P218">
         <v>2.054204940795898</v>
       </c>
     </row>
